--- a/Diagrams/Gantt chart/專案甘特圖.xlsx
+++ b/Diagrams/Gantt chart/專案甘特圖.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\Diagrams\Gantt chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6894267E-01D8-4E42-A548-4EA1F97F941D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AB2FD5-A476-46B4-93BA-5A6EF438F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC956E1D-17AA-4CE2-B07B-3D8F95ED7E8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="2026年" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -542,11 +542,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -561,158 +561,146 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,2431 +1049,2430 @@
   <dimension ref="A1:AW66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="11" customWidth="1"/>
-    <col min="2" max="49" width="2.375" style="15" customWidth="1"/>
-    <col min="50" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="18.375" style="8" customWidth="1"/>
+    <col min="2" max="49" width="2.375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="56" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
-      <c r="AD1" s="48"/>
-      <c r="AE1" s="48"/>
-      <c r="AF1" s="48"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="48"/>
-      <c r="AI1" s="48"/>
-      <c r="AJ1" s="48"/>
-      <c r="AK1" s="48"/>
-      <c r="AL1" s="48"/>
-      <c r="AM1" s="48"/>
-      <c r="AN1" s="48"/>
-      <c r="AO1" s="48"/>
-      <c r="AP1" s="48"/>
-      <c r="AQ1" s="48"/>
-      <c r="AR1" s="48"/>
-      <c r="AS1" s="48"/>
-      <c r="AT1" s="48"/>
-      <c r="AU1" s="48"/>
-      <c r="AV1" s="48"/>
-      <c r="AW1" s="48"/>
-    </row>
-    <row r="2" spans="1:49" s="56" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
+      <c r="AV1" s="49"/>
+      <c r="AW1" s="49"/>
+    </row>
+    <row r="2" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50" t="s">
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50" t="s">
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50" t="s">
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50" t="s">
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="50" t="s">
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="50"/>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="50" t="s">
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50" t="s">
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="51"/>
-    </row>
-    <row r="3" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="51"/>
+      <c r="AW2" s="52"/>
+    </row>
+    <row r="3" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="8"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="8"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="6"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="27"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="21"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="8"/>
+      <c r="Y3" s="6"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
-      <c r="AG3" s="8"/>
+      <c r="AG3" s="6"/>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
-      <c r="AK3" s="8"/>
+      <c r="AK3" s="6"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
-      <c r="AO3" s="8"/>
+      <c r="AO3" s="6"/>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
-      <c r="AS3" s="8"/>
+      <c r="AS3" s="6"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="9"/>
+    <row r="4" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="9"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="7"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="28"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="22"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="9"/>
+      <c r="Y4" s="7"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
-      <c r="AC4" s="9"/>
+      <c r="AC4" s="7"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
-      <c r="AG4" s="9"/>
+      <c r="AG4" s="7"/>
       <c r="AH4" s="2"/>
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
-      <c r="AK4" s="9"/>
+      <c r="AK4" s="7"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
-      <c r="AO4" s="9"/>
+      <c r="AO4" s="7"/>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2"/>
       <c r="AR4" s="2"/>
-      <c r="AS4" s="9"/>
+      <c r="AS4" s="7"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="4"/>
     </row>
-    <row r="5" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="21"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="8"/>
+      <c r="M5" s="6"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="8"/>
+      <c r="Q5" s="6"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="29"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="23"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="8"/>
+      <c r="Y5" s="6"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="6"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
-      <c r="AG5" s="8"/>
+      <c r="AG5" s="6"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="8"/>
+      <c r="AK5" s="6"/>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
-      <c r="AO5" s="8"/>
+      <c r="AO5" s="6"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
-      <c r="AS5" s="8"/>
+      <c r="AS5" s="6"/>
       <c r="AT5" s="1"/>
       <c r="AU5" s="1"/>
       <c r="AV5" s="1"/>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
+    <row r="6" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="9"/>
+      <c r="Q6" s="7"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="28"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="22"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="9"/>
+      <c r="Y6" s="7"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="9"/>
+      <c r="AC6" s="7"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
-      <c r="AG6" s="9"/>
+      <c r="AG6" s="7"/>
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
-      <c r="AK6" s="9"/>
+      <c r="AK6" s="7"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
-      <c r="AO6" s="9"/>
+      <c r="AO6" s="7"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2"/>
       <c r="AR6" s="2"/>
-      <c r="AS6" s="9"/>
+      <c r="AS6" s="7"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="4"/>
     </row>
-    <row r="7" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="48" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="6"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="29"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="23"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="8"/>
+      <c r="Y7" s="6"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="6"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="8"/>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
-      <c r="AK7" s="8"/>
+      <c r="AK7" s="6"/>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
-      <c r="AO7" s="8"/>
+      <c r="AO7" s="6"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="1"/>
-      <c r="AS7" s="8"/>
+      <c r="AS7" s="6"/>
       <c r="AT7" s="1"/>
       <c r="AU7" s="1"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="9"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="7"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="28"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="22"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="9"/>
+      <c r="Y8" s="7"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
-      <c r="AC8" s="9"/>
+      <c r="AC8" s="7"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
-      <c r="AG8" s="9"/>
+      <c r="AG8" s="7"/>
       <c r="AH8" s="2"/>
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2"/>
-      <c r="AK8" s="9"/>
+      <c r="AK8" s="7"/>
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
-      <c r="AO8" s="9"/>
+      <c r="AO8" s="7"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
       <c r="AR8" s="2"/>
-      <c r="AS8" s="9"/>
+      <c r="AS8" s="7"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="4"/>
     </row>
-    <row r="9" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="16"/>
-      <c r="AN9" s="16"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="16"/>
-      <c r="AQ9" s="16"/>
-      <c r="AR9" s="16"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="16"/>
-      <c r="AU9" s="16"/>
-      <c r="AV9" s="16"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="11"/>
+      <c r="AU9" s="11"/>
+      <c r="AV9" s="11"/>
       <c r="AW9" s="3"/>
     </row>
-    <row r="10" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="36"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="36"/>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="35"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="35"/>
-      <c r="AS10" s="36"/>
-      <c r="AT10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="39"/>
-    </row>
-    <row r="11" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+    <row r="10" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="27"/>
+      <c r="AE10" s="27"/>
+      <c r="AF10" s="27"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="27"/>
+      <c r="AI10" s="27"/>
+      <c r="AJ10" s="27"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="27"/>
+      <c r="AM10" s="27"/>
+      <c r="AN10" s="27"/>
+      <c r="AO10" s="28"/>
+      <c r="AP10" s="27"/>
+      <c r="AQ10" s="27"/>
+      <c r="AR10" s="27"/>
+      <c r="AS10" s="28"/>
+      <c r="AT10" s="27"/>
+      <c r="AU10" s="27"/>
+      <c r="AV10" s="27"/>
+      <c r="AW10" s="31"/>
+    </row>
+    <row r="11" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="8"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="24"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="18"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="8"/>
+      <c r="Q11" s="6"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="29"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="23"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="8"/>
+      <c r="Y11" s="6"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="8"/>
+      <c r="AG11" s="6"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="8"/>
+      <c r="AK11" s="6"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
-      <c r="AO11" s="8"/>
+      <c r="AO11" s="6"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
-      <c r="AS11" s="8"/>
+      <c r="AS11" s="6"/>
       <c r="AT11" s="1"/>
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
+    <row r="12" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="45"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="23"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
-      <c r="Q12" s="9"/>
+      <c r="Q12" s="7"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="28"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="22"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Y12" s="9"/>
+      <c r="Y12" s="7"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
-      <c r="AC12" s="9"/>
+      <c r="AC12" s="7"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
-      <c r="AG12" s="9"/>
+      <c r="AG12" s="7"/>
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12" s="2"/>
-      <c r="AK12" s="9"/>
+      <c r="AK12" s="7"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
-      <c r="AO12" s="9"/>
+      <c r="AO12" s="7"/>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
       <c r="AR12" s="2"/>
-      <c r="AS12" s="9"/>
+      <c r="AS12" s="7"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="4"/>
     </row>
-    <row r="13" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+    <row r="13" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="8"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="8"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="6"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="29"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="23"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="8"/>
+      <c r="Y13" s="6"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
-      <c r="AG13" s="8"/>
+      <c r="AG13" s="6"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
-      <c r="AK13" s="8"/>
+      <c r="AK13" s="6"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
-      <c r="AO13" s="8"/>
+      <c r="AO13" s="6"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
-      <c r="AS13" s="8"/>
+      <c r="AS13" s="6"/>
       <c r="AT13" s="1"/>
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53"/>
+    <row r="14" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="45"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="9"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="9"/>
+      <c r="Q14" s="7"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="28"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="22"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
-      <c r="Y14" s="9"/>
+      <c r="Y14" s="7"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
-      <c r="AC14" s="9"/>
+      <c r="AC14" s="7"/>
       <c r="AD14" s="2"/>
       <c r="AE14" s="2"/>
       <c r="AF14" s="2"/>
-      <c r="AG14" s="9"/>
+      <c r="AG14" s="7"/>
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
-      <c r="AK14" s="9"/>
+      <c r="AK14" s="7"/>
       <c r="AL14" s="2"/>
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
-      <c r="AO14" s="9"/>
+      <c r="AO14" s="7"/>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2"/>
       <c r="AR14" s="2"/>
-      <c r="AS14" s="9"/>
+      <c r="AS14" s="7"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="4"/>
     </row>
-    <row r="15" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+    <row r="15" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="16"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
-      <c r="AK15" s="17"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="16"/>
-      <c r="AN15" s="16"/>
-      <c r="AO15" s="17"/>
-      <c r="AP15" s="16"/>
-      <c r="AQ15" s="16"/>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="16"/>
-      <c r="AU15" s="16"/>
-      <c r="AV15" s="16"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
+      <c r="AF15" s="11"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="11"/>
+      <c r="AI15" s="11"/>
+      <c r="AJ15" s="11"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="11"/>
+      <c r="AM15" s="11"/>
+      <c r="AN15" s="11"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="11"/>
+      <c r="AQ15" s="11"/>
+      <c r="AR15" s="11"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="11"/>
+      <c r="AU15" s="11"/>
+      <c r="AV15" s="11"/>
       <c r="AW15" s="3"/>
     </row>
-    <row r="16" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="36"/>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="36"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="39"/>
-    </row>
-    <row r="17" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="16" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16" s="27"/>
+      <c r="AI16" s="27"/>
+      <c r="AJ16" s="27"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="27"/>
+      <c r="AM16" s="27"/>
+      <c r="AN16" s="27"/>
+      <c r="AO16" s="28"/>
+      <c r="AP16" s="27"/>
+      <c r="AQ16" s="27"/>
+      <c r="AR16" s="27"/>
+      <c r="AS16" s="28"/>
+      <c r="AT16" s="27"/>
+      <c r="AU16" s="27"/>
+      <c r="AV16" s="27"/>
+      <c r="AW16" s="31"/>
+    </row>
+    <row r="17" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="6"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
-      <c r="AG17" s="8"/>
+      <c r="AG17" s="6"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
-      <c r="AK17" s="8"/>
+      <c r="AK17" s="6"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
-      <c r="AO17" s="8"/>
+      <c r="AO17" s="6"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
-      <c r="AS17" s="8"/>
+      <c r="AS17" s="6"/>
       <c r="AT17" s="1"/>
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="5"/>
     </row>
-    <row r="18" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+    <row r="18" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="42"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="31"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="25"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
-      <c r="Y18" s="9"/>
+      <c r="Y18" s="7"/>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
-      <c r="AC18" s="9"/>
+      <c r="AC18" s="7"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
-      <c r="AG18" s="9"/>
+      <c r="AG18" s="7"/>
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
       <c r="AJ18" s="2"/>
-      <c r="AK18" s="9"/>
+      <c r="AK18" s="7"/>
       <c r="AL18" s="2"/>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
-      <c r="AO18" s="9"/>
+      <c r="AO18" s="7"/>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="2"/>
       <c r="AR18" s="2"/>
-      <c r="AS18" s="9"/>
+      <c r="AS18" s="7"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="4"/>
     </row>
-    <row r="19" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="8"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="8"/>
+      <c r="I19" s="6"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="8"/>
+      <c r="M19" s="6"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="29"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="23"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="8"/>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="6"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AG19" s="8"/>
+      <c r="AG19" s="6"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
-      <c r="AK19" s="8"/>
+      <c r="AK19" s="6"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
-      <c r="AO19" s="8"/>
+      <c r="AO19" s="6"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
-      <c r="AS19" s="8"/>
+      <c r="AS19" s="6"/>
       <c r="AT19" s="1"/>
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="5"/>
     </row>
-    <row r="20" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+    <row r="20" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="42"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="9"/>
+      <c r="I20" s="7"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
-      <c r="M20" s="9"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="28"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="22"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
-      <c r="Y20" s="9"/>
+      <c r="Y20" s="7"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
-      <c r="AC20" s="9"/>
+      <c r="AC20" s="7"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
-      <c r="AG20" s="9"/>
+      <c r="AG20" s="7"/>
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
-      <c r="AK20" s="9"/>
+      <c r="AK20" s="7"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
-      <c r="AO20" s="9"/>
+      <c r="AO20" s="7"/>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
       <c r="AR20" s="2"/>
-      <c r="AS20" s="9"/>
+      <c r="AS20" s="7"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="4"/>
     </row>
-    <row r="21" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
-      <c r="AC21" s="17"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="17"/>
-      <c r="AH21" s="16"/>
-      <c r="AI21" s="16"/>
-      <c r="AJ21" s="16"/>
-      <c r="AK21" s="17"/>
-      <c r="AL21" s="16"/>
-      <c r="AM21" s="16"/>
-      <c r="AN21" s="16"/>
-      <c r="AO21" s="17"/>
-      <c r="AP21" s="16"/>
-      <c r="AQ21" s="16"/>
-      <c r="AR21" s="16"/>
-      <c r="AS21" s="17"/>
-      <c r="AT21" s="16"/>
-      <c r="AU21" s="16"/>
-      <c r="AV21" s="16"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="11"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="11"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="11"/>
+      <c r="AI21" s="11"/>
+      <c r="AJ21" s="11"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="11"/>
+      <c r="AM21" s="11"/>
+      <c r="AN21" s="11"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="11"/>
+      <c r="AQ21" s="11"/>
+      <c r="AR21" s="11"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="11"/>
+      <c r="AU21" s="11"/>
+      <c r="AV21" s="11"/>
       <c r="AW21" s="3"/>
     </row>
-    <row r="22" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
-      <c r="T22" s="37"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="35"/>
-      <c r="AE22" s="35"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="36"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="35"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="36"/>
-      <c r="AL22" s="35"/>
-      <c r="AM22" s="35"/>
-      <c r="AN22" s="35"/>
-      <c r="AO22" s="36"/>
-      <c r="AP22" s="35"/>
-      <c r="AQ22" s="35"/>
-      <c r="AR22" s="35"/>
-      <c r="AS22" s="36"/>
-      <c r="AT22" s="35"/>
-      <c r="AU22" s="35"/>
-      <c r="AV22" s="35"/>
-      <c r="AW22" s="39"/>
-    </row>
-    <row r="23" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+    <row r="22" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="43"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="27"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="28"/>
+      <c r="AH22" s="27"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="27"/>
+      <c r="AK22" s="28"/>
+      <c r="AL22" s="27"/>
+      <c r="AM22" s="27"/>
+      <c r="AN22" s="27"/>
+      <c r="AO22" s="28"/>
+      <c r="AP22" s="27"/>
+      <c r="AQ22" s="27"/>
+      <c r="AR22" s="27"/>
+      <c r="AS22" s="28"/>
+      <c r="AT22" s="27"/>
+      <c r="AU22" s="27"/>
+      <c r="AV22" s="27"/>
+      <c r="AW22" s="31"/>
+    </row>
+    <row r="23" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="8"/>
+      <c r="I23" s="6"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="29"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="23"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="8"/>
+      <c r="Y23" s="6"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="6"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AG23" s="8"/>
+      <c r="AG23" s="6"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
-      <c r="AK23" s="8"/>
+      <c r="AK23" s="6"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
-      <c r="AO23" s="8"/>
+      <c r="AO23" s="6"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
-      <c r="AS23" s="8"/>
+      <c r="AS23" s="6"/>
       <c r="AT23" s="1"/>
       <c r="AU23" s="1"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="5"/>
     </row>
-    <row r="24" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+    <row r="24" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="45"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="9"/>
+      <c r="I24" s="7"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
       <c r="P24" s="2"/>
-      <c r="Q24" s="9"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="28"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="22"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
-      <c r="Y24" s="9"/>
+      <c r="Y24" s="7"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
-      <c r="AC24" s="9"/>
+      <c r="AC24" s="7"/>
       <c r="AD24" s="2"/>
       <c r="AE24" s="2"/>
       <c r="AF24" s="2"/>
-      <c r="AG24" s="9"/>
+      <c r="AG24" s="7"/>
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2"/>
-      <c r="AK24" s="9"/>
+      <c r="AK24" s="7"/>
       <c r="AL24" s="2"/>
       <c r="AM24" s="2"/>
       <c r="AN24" s="2"/>
-      <c r="AO24" s="9"/>
+      <c r="AO24" s="7"/>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="2"/>
       <c r="AR24" s="2"/>
-      <c r="AS24" s="9"/>
+      <c r="AS24" s="7"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="4"/>
     </row>
-    <row r="25" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+    <row r="25" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="17"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="16"/>
-      <c r="AF25" s="16"/>
-      <c r="AG25" s="17"/>
-      <c r="AH25" s="16"/>
-      <c r="AI25" s="16"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="17"/>
-      <c r="AL25" s="16"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="17"/>
-      <c r="AP25" s="16"/>
-      <c r="AQ25" s="16"/>
-      <c r="AR25" s="16"/>
-      <c r="AS25" s="17"/>
-      <c r="AT25" s="16"/>
-      <c r="AU25" s="16"/>
-      <c r="AV25" s="16"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="12"/>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="12"/>
+      <c r="AH25" s="11"/>
+      <c r="AI25" s="11"/>
+      <c r="AJ25" s="11"/>
+      <c r="AK25" s="12"/>
+      <c r="AL25" s="11"/>
+      <c r="AM25" s="11"/>
+      <c r="AN25" s="11"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="11"/>
+      <c r="AQ25" s="11"/>
+      <c r="AR25" s="11"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="11"/>
+      <c r="AU25" s="11"/>
+      <c r="AV25" s="11"/>
       <c r="AW25" s="3"/>
     </row>
-    <row r="26" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
+    <row r="26" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="46"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="6"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="8"/>
+      <c r="I26" s="6"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="8"/>
+      <c r="Q26" s="6"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="29"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="23"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="8"/>
+      <c r="Y26" s="6"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="6"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AG26" s="8"/>
+      <c r="AG26" s="6"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
-      <c r="AK26" s="8"/>
+      <c r="AK26" s="6"/>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
-      <c r="AO26" s="8"/>
+      <c r="AO26" s="6"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
-      <c r="AS26" s="8"/>
+      <c r="AS26" s="6"/>
       <c r="AT26" s="1"/>
       <c r="AU26" s="1"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="5"/>
     </row>
-    <row r="27" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+    <row r="27" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="20"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="16"/>
-      <c r="AI27" s="16"/>
-      <c r="AJ27" s="16"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="16"/>
-      <c r="AM27" s="16"/>
-      <c r="AN27" s="16"/>
-      <c r="AO27" s="17"/>
-      <c r="AP27" s="16"/>
-      <c r="AQ27" s="16"/>
-      <c r="AR27" s="16"/>
-      <c r="AS27" s="17"/>
-      <c r="AT27" s="16"/>
-      <c r="AU27" s="16"/>
-      <c r="AV27" s="16"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="11"/>
+      <c r="AI27" s="11"/>
+      <c r="AJ27" s="11"/>
+      <c r="AK27" s="12"/>
+      <c r="AL27" s="11"/>
+      <c r="AM27" s="11"/>
+      <c r="AN27" s="11"/>
+      <c r="AO27" s="12"/>
+      <c r="AP27" s="11"/>
+      <c r="AQ27" s="11"/>
+      <c r="AR27" s="11"/>
+      <c r="AS27" s="12"/>
+      <c r="AT27" s="11"/>
+      <c r="AU27" s="11"/>
+      <c r="AV27" s="11"/>
       <c r="AW27" s="3"/>
     </row>
-    <row r="28" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="54"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="36"/>
-      <c r="AD28" s="35"/>
-      <c r="AE28" s="35"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="36"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="35"/>
-      <c r="AJ28" s="35"/>
-      <c r="AK28" s="36"/>
-      <c r="AL28" s="35"/>
-      <c r="AM28" s="35"/>
-      <c r="AN28" s="35"/>
-      <c r="AO28" s="36"/>
-      <c r="AP28" s="35"/>
-      <c r="AQ28" s="35"/>
-      <c r="AR28" s="35"/>
-      <c r="AS28" s="36"/>
-      <c r="AT28" s="35"/>
-      <c r="AU28" s="35"/>
-      <c r="AV28" s="35"/>
-      <c r="AW28" s="39"/>
-    </row>
-    <row r="29" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="28" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="27"/>
+      <c r="AE28" s="27"/>
+      <c r="AF28" s="27"/>
+      <c r="AG28" s="28"/>
+      <c r="AH28" s="27"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="28"/>
+      <c r="AL28" s="27"/>
+      <c r="AM28" s="27"/>
+      <c r="AN28" s="27"/>
+      <c r="AO28" s="28"/>
+      <c r="AP28" s="27"/>
+      <c r="AQ28" s="27"/>
+      <c r="AR28" s="27"/>
+      <c r="AS28" s="28"/>
+      <c r="AT28" s="27"/>
+      <c r="AU28" s="27"/>
+      <c r="AV28" s="27"/>
+      <c r="AW28" s="31"/>
+    </row>
+    <row r="29" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="48" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="8"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="8"/>
+      <c r="I29" s="6"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="32"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="26"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="8"/>
+      <c r="Y29" s="6"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="6"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="8"/>
+      <c r="AG29" s="6"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
-      <c r="AK29" s="8"/>
+      <c r="AK29" s="6"/>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
-      <c r="AO29" s="8"/>
+      <c r="AO29" s="6"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
-      <c r="AS29" s="8"/>
+      <c r="AS29" s="6"/>
       <c r="AT29" s="1"/>
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
       <c r="AW29" s="5"/>
     </row>
-    <row r="30" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="9"/>
+      <c r="E30" s="7"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="28"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="22"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
-      <c r="Y30" s="9"/>
+      <c r="Y30" s="7"/>
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
-      <c r="AC30" s="9"/>
+      <c r="AC30" s="7"/>
       <c r="AD30" s="2"/>
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
-      <c r="AG30" s="9"/>
+      <c r="AG30" s="7"/>
       <c r="AH30" s="2"/>
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
-      <c r="AK30" s="9"/>
+      <c r="AK30" s="7"/>
       <c r="AL30" s="2"/>
       <c r="AM30" s="2"/>
       <c r="AN30" s="2"/>
-      <c r="AO30" s="9"/>
+      <c r="AO30" s="7"/>
       <c r="AP30" s="2"/>
       <c r="AQ30" s="2"/>
       <c r="AR30" s="2"/>
-      <c r="AS30" s="9"/>
+      <c r="AS30" s="7"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="4"/>
     </row>
-    <row r="31" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="8"/>
+      <c r="I31" s="6"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="29"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="23"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="8"/>
+      <c r="Y31" s="6"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="8"/>
+      <c r="AG31" s="6"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
-      <c r="AK31" s="8"/>
+      <c r="AK31" s="6"/>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
       <c r="AN31" s="1"/>
-      <c r="AO31" s="8"/>
+      <c r="AO31" s="6"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
-      <c r="AS31" s="8"/>
+      <c r="AS31" s="6"/>
       <c r="AT31" s="1"/>
       <c r="AU31" s="1"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="5"/>
     </row>
-    <row r="32" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
+    <row r="32" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="42"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="9"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="9"/>
+      <c r="I32" s="7"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="28"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="22"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
-      <c r="Y32" s="9"/>
+      <c r="Y32" s="7"/>
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
-      <c r="AC32" s="9"/>
+      <c r="AC32" s="7"/>
       <c r="AD32" s="2"/>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
-      <c r="AG32" s="9"/>
+      <c r="AG32" s="7"/>
       <c r="AH32" s="2"/>
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
-      <c r="AK32" s="9"/>
+      <c r="AK32" s="7"/>
       <c r="AL32" s="2"/>
       <c r="AM32" s="2"/>
       <c r="AN32" s="2"/>
-      <c r="AO32" s="9"/>
+      <c r="AO32" s="7"/>
       <c r="AP32" s="2"/>
       <c r="AQ32" s="2"/>
       <c r="AR32" s="2"/>
-      <c r="AS32" s="9"/>
+      <c r="AS32" s="7"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="4"/>
     </row>
-    <row r="33" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="42" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="8"/>
+      <c r="I33" s="6"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="8"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="6"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="29"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="23"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="8"/>
+      <c r="Y33" s="6"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="6"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="8"/>
+      <c r="AG33" s="6"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
-      <c r="AK33" s="8"/>
+      <c r="AK33" s="6"/>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1"/>
-      <c r="AO33" s="8"/>
+      <c r="AO33" s="6"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
-      <c r="AS33" s="8"/>
+      <c r="AS33" s="6"/>
       <c r="AT33" s="1"/>
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="5"/>
     </row>
-    <row r="34" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
+    <row r="34" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="42"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="9"/>
+      <c r="E34" s="7"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="9"/>
+      <c r="I34" s="7"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="9"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="7"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="28"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="22"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
-      <c r="Y34" s="9"/>
+      <c r="Y34" s="7"/>
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
-      <c r="AC34" s="9"/>
+      <c r="AC34" s="7"/>
       <c r="AD34" s="2"/>
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
-      <c r="AG34" s="9"/>
+      <c r="AG34" s="7"/>
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
-      <c r="AK34" s="9"/>
+      <c r="AK34" s="7"/>
       <c r="AL34" s="2"/>
       <c r="AM34" s="2"/>
       <c r="AN34" s="2"/>
-      <c r="AO34" s="9"/>
+      <c r="AO34" s="7"/>
       <c r="AP34" s="2"/>
       <c r="AQ34" s="2"/>
       <c r="AR34" s="2"/>
-      <c r="AS34" s="9"/>
+      <c r="AS34" s="7"/>
       <c r="AT34" s="2"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="4"/>
     </row>
-    <row r="35" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
         <v>26</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="8"/>
+      <c r="I35" s="6"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="6"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="8"/>
+      <c r="AG35" s="6"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
-      <c r="AK35" s="8"/>
+      <c r="AK35" s="6"/>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
       <c r="AN35" s="1"/>
-      <c r="AO35" s="8"/>
+      <c r="AO35" s="6"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
-      <c r="AS35" s="8"/>
+      <c r="AS35" s="6"/>
       <c r="AT35" s="1"/>
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="5"/>
     </row>
-    <row r="36" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
+    <row r="36" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="42"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="9"/>
+      <c r="E36" s="7"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="9"/>
+      <c r="I36" s="7"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="31"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="25"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
-      <c r="Y36" s="9"/>
+      <c r="Y36" s="7"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
-      <c r="AC36" s="9"/>
+      <c r="AC36" s="7"/>
       <c r="AD36" s="2"/>
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
-      <c r="AG36" s="9"/>
+      <c r="AG36" s="7"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
-      <c r="AK36" s="9"/>
+      <c r="AK36" s="7"/>
       <c r="AL36" s="2"/>
       <c r="AM36" s="2"/>
       <c r="AN36" s="2"/>
-      <c r="AO36" s="9"/>
+      <c r="AO36" s="7"/>
       <c r="AP36" s="2"/>
       <c r="AQ36" s="2"/>
       <c r="AR36" s="2"/>
-      <c r="AS36" s="9"/>
+      <c r="AS36" s="7"/>
       <c r="AT36" s="2"/>
       <c r="AU36" s="2"/>
       <c r="AV36" s="2"/>
       <c r="AW36" s="4"/>
     </row>
-    <row r="37" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="42" t="s">
         <v>27</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="6"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="8"/>
+      <c r="M37" s="6"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="20"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="24"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
+      <c r="AC37" s="15"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="8"/>
+      <c r="AG37" s="6"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
-      <c r="AK37" s="8"/>
+      <c r="AK37" s="6"/>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
-      <c r="AO37" s="8"/>
+      <c r="AO37" s="6"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
-      <c r="AS37" s="8"/>
+      <c r="AS37" s="6"/>
       <c r="AT37" s="1"/>
       <c r="AU37" s="1"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="5"/>
     </row>
-    <row r="38" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
+    <row r="38" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="42"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="9"/>
+      <c r="E38" s="7"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="9"/>
+      <c r="I38" s="7"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-      <c r="M38" s="9"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-      <c r="Q38" s="9"/>
+      <c r="Q38" s="7"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="28"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="22"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
-      <c r="Y38" s="9"/>
+      <c r="Y38" s="7"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
-      <c r="AC38" s="9"/>
+      <c r="AC38" s="7"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
       <c r="AF38" s="2"/>
-      <c r="AG38" s="9"/>
+      <c r="AG38" s="7"/>
       <c r="AH38" s="2"/>
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
-      <c r="AK38" s="9"/>
+      <c r="AK38" s="7"/>
       <c r="AL38" s="2"/>
       <c r="AM38" s="2"/>
       <c r="AN38" s="2"/>
-      <c r="AO38" s="9"/>
+      <c r="AO38" s="7"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
-      <c r="AS38" s="9"/>
+      <c r="AS38" s="7"/>
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
       <c r="AW38" s="4"/>
     </row>
-    <row r="39" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="42" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="8"/>
+      <c r="I39" s="6"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="8"/>
+      <c r="M39" s="6"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="8"/>
+      <c r="Q39" s="6"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="29"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="23"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="Y39" s="8"/>
+      <c r="Y39" s="6"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="20"/>
-      <c r="AD39" s="20"/>
-      <c r="AE39" s="20"/>
-      <c r="AF39" s="20"/>
-      <c r="AG39" s="20"/>
+      <c r="AB39" s="15"/>
+      <c r="AC39" s="15"/>
+      <c r="AD39" s="15"/>
+      <c r="AE39" s="15"/>
+      <c r="AF39" s="15"/>
+      <c r="AG39" s="15"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
-      <c r="AK39" s="8"/>
+      <c r="AK39" s="6"/>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
-      <c r="AO39" s="8"/>
+      <c r="AO39" s="6"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
       <c r="AR39" s="1"/>
-      <c r="AS39" s="8"/>
+      <c r="AS39" s="6"/>
       <c r="AT39" s="1"/>
       <c r="AU39" s="1"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="5"/>
     </row>
-    <row r="40" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
+    <row r="40" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="42"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="9"/>
+      <c r="E40" s="7"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="9"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-      <c r="M40" s="9"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-      <c r="Q40" s="9"/>
+      <c r="Q40" s="7"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="28"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="22"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
-      <c r="Y40" s="9"/>
+      <c r="Y40" s="7"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
-      <c r="AC40" s="9"/>
+      <c r="AC40" s="7"/>
       <c r="AD40" s="2"/>
       <c r="AE40" s="2"/>
       <c r="AF40" s="2"/>
-      <c r="AG40" s="9"/>
+      <c r="AG40" s="7"/>
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="9"/>
+      <c r="AK40" s="7"/>
       <c r="AL40" s="2"/>
       <c r="AM40" s="2"/>
       <c r="AN40" s="2"/>
-      <c r="AO40" s="9"/>
+      <c r="AO40" s="7"/>
       <c r="AP40" s="2"/>
       <c r="AQ40" s="2"/>
       <c r="AR40" s="2"/>
-      <c r="AS40" s="9"/>
+      <c r="AS40" s="7"/>
       <c r="AT40" s="2"/>
       <c r="AU40" s="2"/>
       <c r="AV40" s="2"/>
       <c r="AW40" s="4"/>
     </row>
-    <row r="41" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="27"/>
-      <c r="W41" s="16"/>
-      <c r="X41" s="16"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="16"/>
-      <c r="AA41" s="16"/>
-      <c r="AB41" s="16"/>
-      <c r="AC41" s="17"/>
-      <c r="AD41" s="16"/>
-      <c r="AE41" s="16"/>
-      <c r="AF41" s="20"/>
-      <c r="AG41" s="20"/>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="20"/>
-      <c r="AJ41" s="20"/>
-      <c r="AK41" s="20"/>
-      <c r="AL41" s="16"/>
-      <c r="AM41" s="16"/>
-      <c r="AN41" s="16"/>
-      <c r="AO41" s="17"/>
-      <c r="AP41" s="16"/>
-      <c r="AQ41" s="16"/>
-      <c r="AR41" s="16"/>
-      <c r="AS41" s="17"/>
-      <c r="AT41" s="16"/>
-      <c r="AU41" s="16"/>
-      <c r="AV41" s="16"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="12"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11"/>
+      <c r="AB41" s="11"/>
+      <c r="AC41" s="12"/>
+      <c r="AD41" s="11"/>
+      <c r="AE41" s="11"/>
+      <c r="AF41" s="15"/>
+      <c r="AG41" s="15"/>
+      <c r="AH41" s="15"/>
+      <c r="AI41" s="15"/>
+      <c r="AJ41" s="15"/>
+      <c r="AK41" s="15"/>
+      <c r="AL41" s="11"/>
+      <c r="AM41" s="11"/>
+      <c r="AN41" s="11"/>
+      <c r="AO41" s="12"/>
+      <c r="AP41" s="11"/>
+      <c r="AQ41" s="11"/>
+      <c r="AR41" s="11"/>
+      <c r="AS41" s="12"/>
+      <c r="AT41" s="11"/>
+      <c r="AU41" s="11"/>
+      <c r="AV41" s="11"/>
       <c r="AW41" s="3"/>
     </row>
-    <row r="42" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="34"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="44"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="43"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="43"/>
-      <c r="U42" s="44"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="35"/>
-      <c r="X42" s="35"/>
-      <c r="Y42" s="36"/>
-      <c r="Z42" s="35"/>
-      <c r="AA42" s="35"/>
-      <c r="AB42" s="35"/>
-      <c r="AC42" s="36"/>
-      <c r="AD42" s="35"/>
-      <c r="AE42" s="35"/>
-      <c r="AF42" s="35"/>
-      <c r="AG42" s="36"/>
-      <c r="AH42" s="43"/>
-      <c r="AI42" s="43"/>
-      <c r="AJ42" s="43"/>
-      <c r="AK42" s="44"/>
-      <c r="AL42" s="43"/>
-      <c r="AM42" s="35"/>
-      <c r="AN42" s="35"/>
-      <c r="AO42" s="36"/>
-      <c r="AP42" s="35"/>
-      <c r="AQ42" s="35"/>
-      <c r="AR42" s="35"/>
-      <c r="AS42" s="36"/>
-      <c r="AT42" s="35"/>
-      <c r="AU42" s="35"/>
-      <c r="AV42" s="35"/>
-      <c r="AW42" s="39"/>
-    </row>
-    <row r="43" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="52" t="s">
+    <row r="42" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="43"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="35"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="35"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="38"/>
+      <c r="W42" s="27"/>
+      <c r="X42" s="27"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="27"/>
+      <c r="AA42" s="27"/>
+      <c r="AB42" s="27"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="27"/>
+      <c r="AE42" s="27"/>
+      <c r="AF42" s="27"/>
+      <c r="AG42" s="28"/>
+      <c r="AH42" s="34"/>
+      <c r="AI42" s="34"/>
+      <c r="AJ42" s="34"/>
+      <c r="AK42" s="35"/>
+      <c r="AL42" s="34"/>
+      <c r="AM42" s="27"/>
+      <c r="AN42" s="27"/>
+      <c r="AO42" s="28"/>
+      <c r="AP42" s="27"/>
+      <c r="AQ42" s="27"/>
+      <c r="AR42" s="27"/>
+      <c r="AS42" s="28"/>
+      <c r="AT42" s="27"/>
+      <c r="AU42" s="27"/>
+      <c r="AV42" s="27"/>
+      <c r="AW42" s="31"/>
+    </row>
+    <row r="43" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="44" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="6"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="8"/>
+      <c r="I43" s="6"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="41"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="13"/>
+      <c r="U43" s="13"/>
+      <c r="V43" s="32"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Y43" s="8"/>
+      <c r="Y43" s="6"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="6"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="18"/>
-      <c r="AL43" s="18"/>
+      <c r="AH43" s="13"/>
+      <c r="AI43" s="13"/>
+      <c r="AJ43" s="13"/>
+      <c r="AK43" s="13"/>
+      <c r="AL43" s="13"/>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
-      <c r="AO43" s="8"/>
+      <c r="AO43" s="6"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
-      <c r="AS43" s="8"/>
+      <c r="AS43" s="6"/>
       <c r="AT43" s="1"/>
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="5"/>
     </row>
-    <row r="44" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53"/>
+    <row r="44" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="45"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="7"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="9"/>
+      <c r="I44" s="7"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
-      <c r="T44" s="19"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="28"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="22"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
-      <c r="Y44" s="9"/>
+      <c r="Y44" s="7"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
       <c r="AB44" s="2"/>
-      <c r="AC44" s="9"/>
+      <c r="AC44" s="7"/>
       <c r="AD44" s="2"/>
       <c r="AE44" s="2"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="8"/>
+      <c r="AG44" s="6"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
-      <c r="AK44" s="8"/>
+      <c r="AK44" s="6"/>
       <c r="AL44" s="2"/>
       <c r="AM44" s="2"/>
       <c r="AN44" s="2"/>
-      <c r="AO44" s="9"/>
+      <c r="AO44" s="7"/>
       <c r="AP44" s="2"/>
       <c r="AQ44" s="2"/>
       <c r="AR44" s="2"/>
-      <c r="AS44" s="9"/>
+      <c r="AS44" s="7"/>
       <c r="AT44" s="2"/>
       <c r="AU44" s="2"/>
       <c r="AV44" s="2"/>
       <c r="AW44" s="4"/>
     </row>
-    <row r="45" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53" t="s">
+    <row r="45" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="8"/>
+      <c r="E45" s="6"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="8"/>
+      <c r="I45" s="6"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="8"/>
+      <c r="M45" s="6"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="8"/>
+      <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="20"/>
+      <c r="S45" s="15"/>
+      <c r="T45" s="15"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="24"/>
+      <c r="W45" s="15"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="8"/>
+      <c r="Y45" s="6"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="6"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
-      <c r="AF45" s="16"/>
-      <c r="AG45" s="17"/>
-      <c r="AH45" s="20"/>
-      <c r="AI45" s="20"/>
-      <c r="AJ45" s="20"/>
-      <c r="AK45" s="20"/>
-      <c r="AL45" s="20"/>
+      <c r="AF45" s="11"/>
+      <c r="AG45" s="12"/>
+      <c r="AH45" s="15"/>
+      <c r="AI45" s="15"/>
+      <c r="AJ45" s="15"/>
+      <c r="AK45" s="15"/>
+      <c r="AL45" s="15"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
-      <c r="AO45" s="8"/>
+      <c r="AO45" s="6"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
-      <c r="AS45" s="8"/>
+      <c r="AS45" s="6"/>
       <c r="AT45" s="1"/>
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="5"/>
     </row>
-    <row r="46" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+    <row r="46" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="45"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="9"/>
+      <c r="E46" s="7"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="9"/>
+      <c r="I46" s="7"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
-      <c r="M46" s="9"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
-      <c r="Q46" s="9"/>
+      <c r="Q46" s="7"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
-      <c r="V46" s="31"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="25"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
-      <c r="Y46" s="9"/>
+      <c r="Y46" s="7"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
-      <c r="AC46" s="9"/>
+      <c r="AC46" s="7"/>
       <c r="AD46" s="2"/>
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
-      <c r="AG46" s="9"/>
+      <c r="AG46" s="7"/>
       <c r="AH46" s="2"/>
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
-      <c r="AK46" s="9"/>
+      <c r="AK46" s="7"/>
       <c r="AL46" s="2"/>
       <c r="AM46" s="2"/>
       <c r="AN46" s="2"/>
-      <c r="AO46" s="9"/>
+      <c r="AO46" s="7"/>
       <c r="AP46" s="2"/>
       <c r="AQ46" s="2"/>
       <c r="AR46" s="2"/>
-      <c r="AS46" s="9"/>
+      <c r="AS46" s="7"/>
       <c r="AT46" s="2"/>
       <c r="AU46" s="2"/>
       <c r="AV46" s="2"/>
       <c r="AW46" s="4"/>
     </row>
-    <row r="47" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+    <row r="47" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3506,7 +3493,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="29"/>
+      <c r="V47" s="23"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -3535,8 +3522,8 @@
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
     </row>
-    <row r="48" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+    <row r="48" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3556,12 +3543,12 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="33" t="s">
+      <c r="U48" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
+      <c r="V48" s="41"/>
+      <c r="W48" s="41"/>
+      <c r="X48" s="41"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -3588,8 +3575,8 @@
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
     </row>
-    <row r="49" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+    <row r="49" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="40"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3639,8 +3626,8 @@
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
     </row>
-    <row r="50" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+    <row r="50" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="40"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3690,8 +3677,8 @@
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
     </row>
-    <row r="51" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+    <row r="51" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="40"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3741,8 +3728,8 @@
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
     </row>
-    <row r="52" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+    <row r="52" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="40"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3792,8 +3779,8 @@
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
     </row>
-    <row r="53" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+    <row r="53" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="40"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3843,8 +3830,8 @@
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
     </row>
-    <row r="54" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+    <row r="54" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="40"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3894,8 +3881,8 @@
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
     </row>
-    <row r="55" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+    <row r="55" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="40"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -3945,8 +3932,8 @@
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
     </row>
-    <row r="56" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+    <row r="56" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="40"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -3996,8 +3983,8 @@
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
     </row>
-    <row r="57" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+    <row r="57" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="40"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -4047,8 +4034,8 @@
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
     </row>
-    <row r="58" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+    <row r="58" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="40"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -4098,8 +4085,8 @@
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
     </row>
-    <row r="59" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+    <row r="59" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="40"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -4149,8 +4136,8 @@
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
     </row>
-    <row r="60" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+    <row r="60" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="40"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -4200,8 +4187,8 @@
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
     </row>
-    <row r="61" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+    <row r="61" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="40"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -4251,8 +4238,8 @@
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
     </row>
-    <row r="62" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+    <row r="62" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="40"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -4302,8 +4289,8 @@
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
     </row>
-    <row r="63" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+    <row r="63" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="40"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4353,8 +4340,8 @@
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
     </row>
-    <row r="64" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+    <row r="64" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="40"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4404,8 +4391,8 @@
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
     </row>
-    <row r="65" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+    <row r="65" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="40"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4455,8 +4442,8 @@
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
     </row>
-    <row r="66" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
+    <row r="66" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="40"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4508,6 +4495,41 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="AL2:AO2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AP2:AS2"/>
+    <mergeCell ref="AT2:AW2"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="A63:A64"/>
@@ -4519,41 +4541,6 @@
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AD2:AG2"/>
-    <mergeCell ref="AH2:AK2"/>
-    <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="AP2:AS2"/>
-    <mergeCell ref="AT2:AW2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="V2:Y2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diagrams/Gantt chart/專案甘特圖.xlsx
+++ b/Diagrams/Gantt chart/專案甘特圖.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\Diagrams\Gantt chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AB2FD5-A476-46B4-93BA-5A6EF438F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A91CE24-2D64-495D-9751-7A0A4153C013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC956E1D-17AA-4CE2-B07B-3D8F95ED7E8C}"/>
   </bookViews>
@@ -229,12 +229,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7ECEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF607D8B"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -247,7 +241,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,85 +582,82 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -669,38 +666,41 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,6 +710,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD9E0E3"/>
       <color rgb="FFE2E8EA"/>
       <color rgb="FF607D8B"/>
       <color rgb="FFE7ECEE"/>
@@ -1054,143 +1055,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="49"/>
-      <c r="AP1" s="49"/>
-      <c r="AQ1" s="49"/>
-      <c r="AR1" s="49"/>
-      <c r="AS1" s="49"/>
-      <c r="AT1" s="49"/>
-      <c r="AU1" s="49"/>
-      <c r="AV1" s="49"/>
-      <c r="AW1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
+      <c r="AW1" s="41"/>
     </row>
     <row r="2" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51" t="s">
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51" t="s">
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51" t="s">
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51" t="s">
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51" t="s">
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51" t="s">
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51" t="s">
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51" t="s">
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="51"/>
-      <c r="AS2" s="51"/>
-      <c r="AT2" s="51" t="s">
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AU2" s="51"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="52"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
     </row>
     <row r="3" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1207,7 +1208,7 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="6"/>
-      <c r="V3" s="21"/>
+      <c r="V3" s="19"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="6"/>
@@ -1237,10 +1238,10 @@
       <c r="AW3" s="5"/>
     </row>
     <row r="4" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="7"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1258,7 +1259,7 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="7"/>
-      <c r="V4" s="22"/>
+      <c r="V4" s="20"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="7"/>
@@ -1288,17 +1289,17 @@
       <c r="AW4" s="4"/>
     </row>
     <row r="5" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
       <c r="J5" s="11"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1311,7 +1312,7 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="6"/>
-      <c r="V5" s="23"/>
+      <c r="V5" s="21"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="6"/>
@@ -1341,15 +1342,15 @@
       <c r="AW5" s="5"/>
     </row>
     <row r="6" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1362,7 +1363,7 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="7"/>
-      <c r="V6" s="22"/>
+      <c r="V6" s="20"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="7"/>
@@ -1392,7 +1393,7 @@
       <c r="AW6" s="4"/>
     </row>
     <row r="7" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1"/>
@@ -1403,10 +1404,10 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1415,7 +1416,7 @@
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="6"/>
-      <c r="V7" s="23"/>
+      <c r="V7" s="21"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="6"/>
@@ -1445,7 +1446,7 @@
       <c r="AW7" s="5"/>
     </row>
     <row r="8" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1455,9 +1456,9 @@
       <c r="H8" s="2"/>
       <c r="I8" s="7"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1466,7 +1467,7 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="7"/>
-      <c r="V8" s="22"/>
+      <c r="V8" s="20"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="7"/>
@@ -1496,7 +1497,7 @@
       <c r="AW8" s="4"/>
     </row>
     <row r="9" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="11"/>
@@ -1506,11 +1507,11 @@
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
@@ -1519,7 +1520,7 @@
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
       <c r="U9" s="12"/>
-      <c r="V9" s="21"/>
+      <c r="V9" s="19"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="12"/>
@@ -1549,58 +1550,58 @@
       <c r="AW9" s="3"/>
     </row>
     <row r="10" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="27"/>
-      <c r="AE10" s="27"/>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="28"/>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="27"/>
-      <c r="AK10" s="28"/>
-      <c r="AL10" s="27"/>
-      <c r="AM10" s="27"/>
-      <c r="AN10" s="27"/>
-      <c r="AO10" s="28"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="27"/>
-      <c r="AR10" s="27"/>
-      <c r="AS10" s="28"/>
-      <c r="AT10" s="27"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="31"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="25"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="24"/>
+      <c r="AW10" s="28"/>
     </row>
     <row r="11" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="45" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1"/>
@@ -1611,11 +1612,11 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="18"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="16"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="6"/>
@@ -1623,7 +1624,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="6"/>
-      <c r="V11" s="23"/>
+      <c r="V11" s="21"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="6"/>
@@ -1653,7 +1654,7 @@
       <c r="AW11" s="5"/>
     </row>
     <row r="12" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+      <c r="A12" s="46"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1662,10 +1663,10 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="17"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -1674,7 +1675,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="7"/>
-      <c r="V12" s="22"/>
+      <c r="V12" s="20"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="7"/>
@@ -1704,7 +1705,7 @@
       <c r="AW12" s="4"/>
     </row>
     <row r="13" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="46" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1"/>
@@ -1717,17 +1718,17 @@
       <c r="I13" s="6"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="6"/>
-      <c r="V13" s="23"/>
+      <c r="V13" s="21"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="6"/>
@@ -1757,7 +1758,7 @@
       <c r="AW13" s="5"/>
     </row>
     <row r="14" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1768,9 +1769,9 @@
       <c r="I14" s="7"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="7"/>
@@ -1778,7 +1779,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="7"/>
-      <c r="V14" s="22"/>
+      <c r="V14" s="20"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="7"/>
@@ -1808,7 +1809,7 @@
       <c r="AW14" s="4"/>
     </row>
     <row r="15" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="46" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="11"/>
@@ -1826,12 +1827,12 @@
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
       <c r="U15" s="12"/>
-      <c r="V15" s="21"/>
+      <c r="V15" s="19"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="12"/>
@@ -1862,57 +1863,57 @@
     </row>
     <row r="16" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="27"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="27"/>
-      <c r="AF16" s="27"/>
-      <c r="AG16" s="28"/>
-      <c r="AH16" s="27"/>
-      <c r="AI16" s="27"/>
-      <c r="AJ16" s="27"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="27"/>
-      <c r="AM16" s="27"/>
-      <c r="AN16" s="27"/>
-      <c r="AO16" s="28"/>
-      <c r="AP16" s="27"/>
-      <c r="AQ16" s="27"/>
-      <c r="AR16" s="27"/>
-      <c r="AS16" s="28"/>
-      <c r="AT16" s="27"/>
-      <c r="AU16" s="27"/>
-      <c r="AV16" s="27"/>
-      <c r="AW16" s="31"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="25"/>
+      <c r="AL16" s="24"/>
+      <c r="AM16" s="24"/>
+      <c r="AN16" s="24"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="24"/>
+      <c r="AR16" s="24"/>
+      <c r="AS16" s="25"/>
+      <c r="AT16" s="24"/>
+      <c r="AU16" s="24"/>
+      <c r="AV16" s="24"/>
+      <c r="AW16" s="28"/>
     </row>
     <row r="17" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="36" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1"/>
@@ -1923,22 +1924,22 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="50"/>
+      <c r="U17" s="50"/>
+      <c r="V17" s="51"/>
+      <c r="W17" s="50"/>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="50"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -1965,7 +1966,7 @@
       <c r="AW17" s="5"/>
     </row>
     <row r="18" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1974,19 +1975,19 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="25"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="22"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="7"/>
@@ -2016,7 +2017,7 @@
       <c r="AW18" s="4"/>
     </row>
     <row r="19" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="37" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1"/>
@@ -2034,12 +2035,12 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="6"/>
-      <c r="V19" s="23"/>
+      <c r="V19" s="21"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="6"/>
@@ -2069,7 +2070,7 @@
       <c r="AW19" s="5"/>
     </row>
     <row r="20" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2085,12 +2086,12 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="7"/>
-      <c r="V20" s="22"/>
+      <c r="V20" s="20"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="7"/>
@@ -2120,7 +2121,7 @@
       <c r="AW20" s="4"/>
     </row>
     <row r="21" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="37" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="11"/>
@@ -2138,12 +2139,12 @@
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="21"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="19"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="12"/>
@@ -2173,58 +2174,58 @@
       <c r="AW21" s="3"/>
     </row>
     <row r="22" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="27"/>
-      <c r="AA22" s="27"/>
-      <c r="AB22" s="27"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="27"/>
-      <c r="AE22" s="27"/>
-      <c r="AF22" s="27"/>
-      <c r="AG22" s="28"/>
-      <c r="AH22" s="27"/>
-      <c r="AI22" s="27"/>
-      <c r="AJ22" s="27"/>
-      <c r="AK22" s="28"/>
-      <c r="AL22" s="27"/>
-      <c r="AM22" s="27"/>
-      <c r="AN22" s="27"/>
-      <c r="AO22" s="28"/>
-      <c r="AP22" s="27"/>
-      <c r="AQ22" s="27"/>
-      <c r="AR22" s="27"/>
-      <c r="AS22" s="28"/>
-      <c r="AT22" s="27"/>
-      <c r="AU22" s="27"/>
-      <c r="AV22" s="27"/>
-      <c r="AW22" s="31"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="24"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="24"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="24"/>
+      <c r="AJ22" s="24"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="24"/>
+      <c r="AM22" s="24"/>
+      <c r="AN22" s="24"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="24"/>
+      <c r="AQ22" s="24"/>
+      <c r="AR22" s="24"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="24"/>
+      <c r="AU22" s="24"/>
+      <c r="AV22" s="24"/>
+      <c r="AW22" s="28"/>
     </row>
     <row r="23" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="45" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="1"/>
@@ -2237,17 +2238,17 @@
       <c r="I23" s="6"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="23"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="21"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="6"/>
@@ -2277,7 +2278,7 @@
       <c r="AW23" s="5"/>
     </row>
     <row r="24" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
+      <c r="A24" s="46"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2288,17 +2289,17 @@
       <c r="I24" s="7"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="7"/>
-      <c r="V24" s="22"/>
+      <c r="V24" s="20"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
       <c r="Y24" s="7"/>
@@ -2328,7 +2329,7 @@
       <c r="AW24" s="4"/>
     </row>
     <row r="25" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="46" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="11"/>
@@ -2342,8 +2343,8 @@
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="12"/>
@@ -2351,7 +2352,7 @@
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
       <c r="U25" s="12"/>
-      <c r="V25" s="21"/>
+      <c r="V25" s="19"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
       <c r="Y25" s="12"/>
@@ -2381,7 +2382,7 @@
       <c r="AW25" s="3"/>
     </row>
     <row r="26" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
+      <c r="A26" s="48"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2394,15 +2395,15 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="6"/>
-      <c r="V26" s="23"/>
+      <c r="V26" s="21"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="6"/>
@@ -2432,7 +2433,7 @@
       <c r="AW26" s="5"/>
     </row>
     <row r="27" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="46" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="11"/>
@@ -2447,26 +2448,26 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="49"/>
       <c r="AH27" s="11"/>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="11"/>
@@ -2486,57 +2487,57 @@
     </row>
     <row r="28" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="47"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="27"/>
-      <c r="AE28" s="27"/>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="28"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="28"/>
-      <c r="AL28" s="27"/>
-      <c r="AM28" s="27"/>
-      <c r="AN28" s="27"/>
-      <c r="AO28" s="28"/>
-      <c r="AP28" s="27"/>
-      <c r="AQ28" s="27"/>
-      <c r="AR28" s="27"/>
-      <c r="AS28" s="28"/>
-      <c r="AT28" s="27"/>
-      <c r="AU28" s="27"/>
-      <c r="AV28" s="27"/>
-      <c r="AW28" s="31"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
+      <c r="AB28" s="24"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="24"/>
+      <c r="AE28" s="24"/>
+      <c r="AF28" s="24"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="24"/>
+      <c r="AI28" s="24"/>
+      <c r="AJ28" s="24"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="24"/>
+      <c r="AM28" s="24"/>
+      <c r="AN28" s="24"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="24"/>
+      <c r="AQ28" s="24"/>
+      <c r="AR28" s="24"/>
+      <c r="AS28" s="25"/>
+      <c r="AT28" s="24"/>
+      <c r="AU28" s="24"/>
+      <c r="AV28" s="24"/>
+      <c r="AW28" s="28"/>
     </row>
     <row r="29" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1"/>
@@ -2549,17 +2550,17 @@
       <c r="I29" s="6"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="26"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="23"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="6"/>
@@ -2589,7 +2590,7 @@
       <c r="AW29" s="5"/>
     </row>
     <row r="30" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2600,17 +2601,17 @@
       <c r="I30" s="7"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="22"/>
+      <c r="V30" s="20"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="7"/>
@@ -2640,7 +2641,7 @@
       <c r="AW30" s="4"/>
     </row>
     <row r="31" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="1"/>
@@ -2655,15 +2656,15 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="23"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="49"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="49"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="21"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="6"/>
@@ -2693,7 +2694,7 @@
       <c r="AW31" s="5"/>
     </row>
     <row r="32" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="42"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2706,15 +2707,15 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="22"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="20"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="7"/>
@@ -2744,7 +2745,7 @@
       <c r="AW32" s="4"/>
     </row>
     <row r="33" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="1"/>
@@ -2758,16 +2759,16 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
       <c r="Q33" s="6"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
       <c r="U33" s="6"/>
-      <c r="V33" s="23"/>
+      <c r="V33" s="21"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="6"/>
@@ -2797,7 +2798,7 @@
       <c r="AW33" s="5"/>
     </row>
     <row r="34" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="42"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2809,16 +2810,16 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="7"/>
-      <c r="V34" s="22"/>
+      <c r="V34" s="20"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
       <c r="Y34" s="7"/>
@@ -2848,7 +2849,7 @@
       <c r="AW34" s="4"/>
     </row>
     <row r="35" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="37" t="s">
         <v>26</v>
       </c>
       <c r="B35" s="1"/>
@@ -2862,19 +2863,19 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="24"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="15"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2901,7 +2902,7 @@
       <c r="AW35" s="5"/>
     </row>
     <row r="36" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="42"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2913,16 +2914,16 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="25"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="22"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
       <c r="Y36" s="7"/>
@@ -2952,7 +2953,7 @@
       <c r="AW36" s="4"/>
     </row>
     <row r="37" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="42" t="s">
+      <c r="A37" s="37" t="s">
         <v>27</v>
       </c>
       <c r="B37" s="1"/>
@@ -2971,18 +2972,18 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="24"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="49"/>
+      <c r="Y37" s="49"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="49"/>
+      <c r="AC37" s="49"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
@@ -3005,7 +3006,7 @@
       <c r="AW37" s="5"/>
     </row>
     <row r="38" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="42"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -3026,7 +3027,7 @@
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="22"/>
+      <c r="V38" s="20"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
       <c r="Y38" s="7"/>
@@ -3056,7 +3057,7 @@
       <c r="AW38" s="4"/>
     </row>
     <row r="39" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="42" t="s">
+      <c r="A39" s="37" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="1"/>
@@ -3079,18 +3080,18 @@
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="6"/>
-      <c r="V39" s="23"/>
+      <c r="V39" s="21"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="6"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
-      <c r="AB39" s="15"/>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="15"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="49"/>
+      <c r="AF39" s="49"/>
+      <c r="AG39" s="49"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
@@ -3109,7 +3110,7 @@
       <c r="AW39" s="5"/>
     </row>
     <row r="40" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="42"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -3130,7 +3131,7 @@
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="7"/>
-      <c r="V40" s="22"/>
+      <c r="V40" s="20"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
       <c r="Y40" s="7"/>
@@ -3160,7 +3161,7 @@
       <c r="AW40" s="4"/>
     </row>
     <row r="41" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="42" t="s">
+      <c r="A41" s="37" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="11"/>
@@ -3183,7 +3184,7 @@
       <c r="S41" s="11"/>
       <c r="T41" s="11"/>
       <c r="U41" s="12"/>
-      <c r="V41" s="21"/>
+      <c r="V41" s="19"/>
       <c r="W41" s="11"/>
       <c r="X41" s="11"/>
       <c r="Y41" s="12"/>
@@ -3193,12 +3194,12 @@
       <c r="AC41" s="12"/>
       <c r="AD41" s="11"/>
       <c r="AE41" s="11"/>
-      <c r="AF41" s="15"/>
-      <c r="AG41" s="15"/>
-      <c r="AH41" s="15"/>
-      <c r="AI41" s="15"/>
-      <c r="AJ41" s="15"/>
-      <c r="AK41" s="15"/>
+      <c r="AF41" s="49"/>
+      <c r="AG41" s="49"/>
+      <c r="AH41" s="49"/>
+      <c r="AI41" s="49"/>
+      <c r="AJ41" s="49"/>
+      <c r="AK41" s="49"/>
       <c r="AL41" s="11"/>
       <c r="AM41" s="11"/>
       <c r="AN41" s="11"/>
@@ -3213,58 +3214,58 @@
       <c r="AW41" s="3"/>
     </row>
     <row r="42" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="43"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="35"/>
-      <c r="V42" s="38"/>
-      <c r="W42" s="27"/>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="27"/>
-      <c r="AA42" s="27"/>
-      <c r="AB42" s="27"/>
-      <c r="AC42" s="28"/>
-      <c r="AD42" s="27"/>
-      <c r="AE42" s="27"/>
-      <c r="AF42" s="27"/>
-      <c r="AG42" s="28"/>
-      <c r="AH42" s="34"/>
-      <c r="AI42" s="34"/>
-      <c r="AJ42" s="34"/>
-      <c r="AK42" s="35"/>
-      <c r="AL42" s="34"/>
-      <c r="AM42" s="27"/>
-      <c r="AN42" s="27"/>
-      <c r="AO42" s="28"/>
-      <c r="AP42" s="27"/>
-      <c r="AQ42" s="27"/>
-      <c r="AR42" s="27"/>
-      <c r="AS42" s="28"/>
-      <c r="AT42" s="27"/>
-      <c r="AU42" s="27"/>
-      <c r="AV42" s="27"/>
-      <c r="AW42" s="31"/>
+      <c r="A42" s="38"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="24"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="31"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="25"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
+      <c r="AR42" s="24"/>
+      <c r="AS42" s="25"/>
+      <c r="AT42" s="24"/>
+      <c r="AU42" s="24"/>
+      <c r="AV42" s="24"/>
+      <c r="AW42" s="28"/>
     </row>
     <row r="43" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="45" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1"/>
@@ -3278,16 +3279,16 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
-      <c r="R43" s="13"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="13"/>
-      <c r="U43" s="13"/>
-      <c r="V43" s="32"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="51"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="6"/>
@@ -3299,11 +3300,11 @@
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
-      <c r="AH43" s="13"/>
-      <c r="AI43" s="13"/>
-      <c r="AJ43" s="13"/>
-      <c r="AK43" s="13"/>
-      <c r="AL43" s="13"/>
+      <c r="AH43" s="50"/>
+      <c r="AI43" s="50"/>
+      <c r="AJ43" s="50"/>
+      <c r="AK43" s="50"/>
+      <c r="AL43" s="50"/>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
       <c r="AO43" s="6"/>
@@ -3317,7 +3318,7 @@
       <c r="AW43" s="5"/>
     </row>
     <row r="44" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="45"/>
+      <c r="A44" s="46"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -3329,16 +3330,16 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="22"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
+      <c r="R44" s="13"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="13"/>
+      <c r="U44" s="13"/>
+      <c r="V44" s="20"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
       <c r="Y44" s="7"/>
@@ -3368,7 +3369,7 @@
       <c r="AW44" s="4"/>
     </row>
     <row r="45" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="46" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="1"/>
@@ -3388,11 +3389,11 @@
       <c r="P45" s="1"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="24"/>
-      <c r="W45" s="15"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="49"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="6"/>
       <c r="Z45" s="1"/>
@@ -3403,11 +3404,11 @@
       <c r="AE45" s="1"/>
       <c r="AF45" s="11"/>
       <c r="AG45" s="12"/>
-      <c r="AH45" s="15"/>
-      <c r="AI45" s="15"/>
-      <c r="AJ45" s="15"/>
-      <c r="AK45" s="15"/>
-      <c r="AL45" s="15"/>
+      <c r="AH45" s="49"/>
+      <c r="AI45" s="49"/>
+      <c r="AJ45" s="49"/>
+      <c r="AK45" s="49"/>
+      <c r="AL45" s="49"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
       <c r="AO45" s="6"/>
@@ -3421,7 +3422,7 @@
       <c r="AW45" s="5"/>
     </row>
     <row r="46" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="45"/>
+      <c r="A46" s="46"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -3439,10 +3440,10 @@
       <c r="P46" s="2"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="25"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="13"/>
+      <c r="V46" s="22"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
       <c r="Y46" s="7"/>
@@ -3472,7 +3473,7 @@
       <c r="AW46" s="4"/>
     </row>
     <row r="47" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3493,7 +3494,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="23"/>
+      <c r="V47" s="21"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -3523,7 +3524,7 @@
       <c r="AW47" s="1"/>
     </row>
     <row r="48" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3543,12 +3544,12 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="41" t="s">
+      <c r="U48" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="V48" s="41"/>
-      <c r="W48" s="41"/>
-      <c r="X48" s="41"/>
+      <c r="V48" s="40"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="40"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -3576,7 +3577,7 @@
       <c r="AW48" s="1"/>
     </row>
     <row r="49" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="40"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3627,7 +3628,7 @@
       <c r="AW49" s="1"/>
     </row>
     <row r="50" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="40"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3678,7 +3679,7 @@
       <c r="AW50" s="1"/>
     </row>
     <row r="51" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="40"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3729,7 +3730,7 @@
       <c r="AW51" s="1"/>
     </row>
     <row r="52" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="40"/>
+      <c r="A52" s="39"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3780,7 +3781,7 @@
       <c r="AW52" s="1"/>
     </row>
     <row r="53" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
+      <c r="A53" s="39"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3831,7 +3832,7 @@
       <c r="AW53" s="1"/>
     </row>
     <row r="54" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="40"/>
+      <c r="A54" s="39"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3882,7 +3883,7 @@
       <c r="AW54" s="1"/>
     </row>
     <row r="55" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
+      <c r="A55" s="39"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -3933,7 +3934,7 @@
       <c r="AW55" s="1"/>
     </row>
     <row r="56" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="40"/>
+      <c r="A56" s="39"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -3984,7 +3985,7 @@
       <c r="AW56" s="1"/>
     </row>
     <row r="57" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -4035,7 +4036,7 @@
       <c r="AW57" s="1"/>
     </row>
     <row r="58" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="40"/>
+      <c r="A58" s="39"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -4086,7 +4087,7 @@
       <c r="AW58" s="1"/>
     </row>
     <row r="59" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="40"/>
+      <c r="A59" s="39"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -4137,7 +4138,7 @@
       <c r="AW59" s="1"/>
     </row>
     <row r="60" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="40"/>
+      <c r="A60" s="39"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -4188,7 +4189,7 @@
       <c r="AW60" s="1"/>
     </row>
     <row r="61" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="40"/>
+      <c r="A61" s="39"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -4239,7 +4240,7 @@
       <c r="AW61" s="1"/>
     </row>
     <row r="62" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="40"/>
+      <c r="A62" s="39"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -4290,7 +4291,7 @@
       <c r="AW62" s="1"/>
     </row>
     <row r="63" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="40"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4341,7 +4342,7 @@
       <c r="AW63" s="1"/>
     </row>
     <row r="64" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="40"/>
+      <c r="A64" s="39"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4392,7 +4393,7 @@
       <c r="AW64" s="1"/>
     </row>
     <row r="65" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="40"/>
+      <c r="A65" s="39"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4443,7 +4444,7 @@
       <c r="AW65" s="1"/>
     </row>
     <row r="66" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="40"/>
+      <c r="A66" s="39"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4495,29 +4496,17 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AD2:AG2"/>
-    <mergeCell ref="AH2:AK2"/>
-    <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="AP2:AS2"/>
-    <mergeCell ref="AT2:AW2"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
@@ -4530,17 +4519,29 @@
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="U48:X48"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AP2:AS2"/>
+    <mergeCell ref="AT2:AW2"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="AL2:AO2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="V2:Y2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diagrams/Gantt chart/專案甘特圖.xlsx
+++ b/Diagrams/Gantt chart/專案甘特圖.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\Diagrams\Gantt chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6894267E-01D8-4E42-A548-4EA1F97F941D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A91CE24-2D64-495D-9751-7A0A4153C013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC956E1D-17AA-4CE2-B07B-3D8F95ED7E8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="2026年" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -229,12 +229,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7ECEE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF607D8B"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -247,7 +241,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E0E3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,11 +542,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -561,158 +561,146 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -722,6 +710,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD9E0E3"/>
       <color rgb="FFE2E8EA"/>
       <color rgb="FF607D8B"/>
       <color rgb="FFE7ECEE"/>
@@ -1061,2431 +1050,2430 @@
   <dimension ref="A1:AW66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.375" style="11" customWidth="1"/>
-    <col min="2" max="49" width="2.375" style="15" customWidth="1"/>
-    <col min="50" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="18.375" style="8" customWidth="1"/>
+    <col min="2" max="49" width="2.375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="56" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
-      <c r="AD1" s="48"/>
-      <c r="AE1" s="48"/>
-      <c r="AF1" s="48"/>
-      <c r="AG1" s="48"/>
-      <c r="AH1" s="48"/>
-      <c r="AI1" s="48"/>
-      <c r="AJ1" s="48"/>
-      <c r="AK1" s="48"/>
-      <c r="AL1" s="48"/>
-      <c r="AM1" s="48"/>
-      <c r="AN1" s="48"/>
-      <c r="AO1" s="48"/>
-      <c r="AP1" s="48"/>
-      <c r="AQ1" s="48"/>
-      <c r="AR1" s="48"/>
-      <c r="AS1" s="48"/>
-      <c r="AT1" s="48"/>
-      <c r="AU1" s="48"/>
-      <c r="AV1" s="48"/>
-      <c r="AW1" s="48"/>
-    </row>
-    <row r="2" spans="1:49" s="56" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="41"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="41"/>
+      <c r="AN1" s="41"/>
+      <c r="AO1" s="41"/>
+      <c r="AP1" s="41"/>
+      <c r="AQ1" s="41"/>
+      <c r="AR1" s="41"/>
+      <c r="AS1" s="41"/>
+      <c r="AT1" s="41"/>
+      <c r="AU1" s="41"/>
+      <c r="AV1" s="41"/>
+      <c r="AW1" s="41"/>
+    </row>
+    <row r="2" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50" t="s">
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50" t="s">
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50" t="s">
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50" t="s">
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50" t="s">
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
-      <c r="AL2" s="50" t="s">
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="50"/>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="50"/>
-      <c r="AP2" s="50" t="s">
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="50"/>
-      <c r="AR2" s="50"/>
-      <c r="AS2" s="50"/>
-      <c r="AT2" s="50" t="s">
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AU2" s="50"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="51"/>
-    </row>
-    <row r="3" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
+    </row>
+    <row r="3" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="8"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="8"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="6"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="27"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="19"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="8"/>
+      <c r="Y3" s="6"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="6"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
-      <c r="AG3" s="8"/>
+      <c r="AG3" s="6"/>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
-      <c r="AK3" s="8"/>
+      <c r="AK3" s="6"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
-      <c r="AO3" s="8"/>
+      <c r="AO3" s="6"/>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
-      <c r="AS3" s="8"/>
+      <c r="AS3" s="6"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
       <c r="AW3" s="5"/>
     </row>
-    <row r="4" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="9"/>
+    <row r="4" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="9"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
-      <c r="Q4" s="9"/>
+      <c r="Q4" s="7"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="28"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="20"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="9"/>
+      <c r="Y4" s="7"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
-      <c r="AC4" s="9"/>
+      <c r="AC4" s="7"/>
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
-      <c r="AG4" s="9"/>
+      <c r="AG4" s="7"/>
       <c r="AH4" s="2"/>
       <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
-      <c r="AK4" s="9"/>
+      <c r="AK4" s="7"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
-      <c r="AO4" s="9"/>
+      <c r="AO4" s="7"/>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2"/>
       <c r="AR4" s="2"/>
-      <c r="AS4" s="9"/>
+      <c r="AS4" s="7"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="4"/>
     </row>
-    <row r="5" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="21"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="8"/>
+      <c r="M5" s="6"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="8"/>
+      <c r="Q5" s="6"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="29"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="21"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="8"/>
+      <c r="Y5" s="6"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="6"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
-      <c r="AG5" s="8"/>
+      <c r="AG5" s="6"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="8"/>
+      <c r="AK5" s="6"/>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
-      <c r="AO5" s="8"/>
+      <c r="AO5" s="6"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
-      <c r="AS5" s="8"/>
+      <c r="AS5" s="6"/>
       <c r="AT5" s="1"/>
       <c r="AU5" s="1"/>
       <c r="AV5" s="1"/>
       <c r="AW5" s="5"/>
     </row>
-    <row r="6" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
+    <row r="6" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="9"/>
+      <c r="Q6" s="7"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="28"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="20"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="9"/>
+      <c r="Y6" s="7"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="9"/>
+      <c r="AC6" s="7"/>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
       <c r="AF6" s="2"/>
-      <c r="AG6" s="9"/>
+      <c r="AG6" s="7"/>
       <c r="AH6" s="2"/>
       <c r="AI6" s="2"/>
       <c r="AJ6" s="2"/>
-      <c r="AK6" s="9"/>
+      <c r="AK6" s="7"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
-      <c r="AO6" s="9"/>
+      <c r="AO6" s="7"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2"/>
       <c r="AR6" s="2"/>
-      <c r="AS6" s="9"/>
+      <c r="AS6" s="7"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="4"/>
     </row>
-    <row r="7" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="6"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="29"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="21"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="8"/>
+      <c r="Y7" s="6"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="6"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="8"/>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
-      <c r="AK7" s="8"/>
+      <c r="AK7" s="6"/>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
-      <c r="AO7" s="8"/>
+      <c r="AO7" s="6"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="1"/>
-      <c r="AS7" s="8"/>
+      <c r="AS7" s="6"/>
       <c r="AT7" s="1"/>
       <c r="AU7" s="1"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="5"/>
     </row>
-    <row r="8" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="9"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
-      <c r="Q8" s="9"/>
+      <c r="Q8" s="7"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="28"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="20"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-      <c r="Y8" s="9"/>
+      <c r="Y8" s="7"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
-      <c r="AC8" s="9"/>
+      <c r="AC8" s="7"/>
       <c r="AD8" s="2"/>
       <c r="AE8" s="2"/>
       <c r="AF8" s="2"/>
-      <c r="AG8" s="9"/>
+      <c r="AG8" s="7"/>
       <c r="AH8" s="2"/>
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2"/>
-      <c r="AK8" s="9"/>
+      <c r="AK8" s="7"/>
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
-      <c r="AO8" s="9"/>
+      <c r="AO8" s="7"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
       <c r="AR8" s="2"/>
-      <c r="AS8" s="9"/>
+      <c r="AS8" s="7"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="4"/>
     </row>
-    <row r="9" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
-      <c r="AJ9" s="16"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="16"/>
-      <c r="AM9" s="16"/>
-      <c r="AN9" s="16"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="16"/>
-      <c r="AQ9" s="16"/>
-      <c r="AR9" s="16"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="16"/>
-      <c r="AU9" s="16"/>
-      <c r="AV9" s="16"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="11"/>
+      <c r="AI9" s="11"/>
+      <c r="AJ9" s="11"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="11"/>
+      <c r="AU9" s="11"/>
+      <c r="AV9" s="11"/>
       <c r="AW9" s="3"/>
     </row>
-    <row r="10" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="36"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="36"/>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="35"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="35"/>
-      <c r="AS10" s="36"/>
-      <c r="AT10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="39"/>
-    </row>
-    <row r="11" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+    <row r="10" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="25"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="24"/>
+      <c r="AW10" s="28"/>
+    </row>
+    <row r="11" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="8"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="24"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="16"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="8"/>
+      <c r="Q11" s="6"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="29"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="21"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="8"/>
+      <c r="Y11" s="6"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="8"/>
+      <c r="AG11" s="6"/>
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
-      <c r="AK11" s="8"/>
+      <c r="AK11" s="6"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
-      <c r="AO11" s="8"/>
+      <c r="AO11" s="6"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
-      <c r="AS11" s="8"/>
+      <c r="AS11" s="6"/>
       <c r="AT11" s="1"/>
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="5"/>
     </row>
-    <row r="12" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
+    <row r="12" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="46"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="23"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
-      <c r="Q12" s="9"/>
+      <c r="Q12" s="7"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="28"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="20"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Y12" s="9"/>
+      <c r="Y12" s="7"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
-      <c r="AC12" s="9"/>
+      <c r="AC12" s="7"/>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2"/>
       <c r="AF12" s="2"/>
-      <c r="AG12" s="9"/>
+      <c r="AG12" s="7"/>
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12" s="2"/>
-      <c r="AK12" s="9"/>
+      <c r="AK12" s="7"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
-      <c r="AO12" s="9"/>
+      <c r="AO12" s="7"/>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
       <c r="AR12" s="2"/>
-      <c r="AS12" s="9"/>
+      <c r="AS12" s="7"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="4"/>
     </row>
-    <row r="13" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+    <row r="13" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="8"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="8"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="6"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="29"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="21"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="8"/>
+      <c r="Y13" s="6"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
-      <c r="AG13" s="8"/>
+      <c r="AG13" s="6"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
-      <c r="AK13" s="8"/>
+      <c r="AK13" s="6"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
-      <c r="AO13" s="8"/>
+      <c r="AO13" s="6"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
-      <c r="AS13" s="8"/>
+      <c r="AS13" s="6"/>
       <c r="AT13" s="1"/>
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="5"/>
     </row>
-    <row r="14" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53"/>
+    <row r="14" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="9"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
-      <c r="Q14" s="9"/>
+      <c r="Q14" s="7"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="28"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="20"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
-      <c r="Y14" s="9"/>
+      <c r="Y14" s="7"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
-      <c r="AC14" s="9"/>
+      <c r="AC14" s="7"/>
       <c r="AD14" s="2"/>
       <c r="AE14" s="2"/>
       <c r="AF14" s="2"/>
-      <c r="AG14" s="9"/>
+      <c r="AG14" s="7"/>
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
-      <c r="AK14" s="9"/>
+      <c r="AK14" s="7"/>
       <c r="AL14" s="2"/>
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
-      <c r="AO14" s="9"/>
+      <c r="AO14" s="7"/>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2"/>
       <c r="AR14" s="2"/>
-      <c r="AS14" s="9"/>
+      <c r="AS14" s="7"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="4"/>
     </row>
-    <row r="15" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+    <row r="15" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="16"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="17"/>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
-      <c r="AK15" s="17"/>
-      <c r="AL15" s="16"/>
-      <c r="AM15" s="16"/>
-      <c r="AN15" s="16"/>
-      <c r="AO15" s="17"/>
-      <c r="AP15" s="16"/>
-      <c r="AQ15" s="16"/>
-      <c r="AR15" s="16"/>
-      <c r="AS15" s="17"/>
-      <c r="AT15" s="16"/>
-      <c r="AU15" s="16"/>
-      <c r="AV15" s="16"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
+      <c r="AF15" s="11"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="11"/>
+      <c r="AI15" s="11"/>
+      <c r="AJ15" s="11"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="11"/>
+      <c r="AM15" s="11"/>
+      <c r="AN15" s="11"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="11"/>
+      <c r="AQ15" s="11"/>
+      <c r="AR15" s="11"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="11"/>
+      <c r="AU15" s="11"/>
+      <c r="AV15" s="11"/>
       <c r="AW15" s="3"/>
     </row>
-    <row r="16" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="36"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="36"/>
-      <c r="AL16" s="35"/>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="36"/>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="35"/>
-      <c r="AR16" s="35"/>
-      <c r="AS16" s="36"/>
-      <c r="AT16" s="35"/>
-      <c r="AU16" s="35"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="39"/>
-    </row>
-    <row r="17" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="16" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="47"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="25"/>
+      <c r="AL16" s="24"/>
+      <c r="AM16" s="24"/>
+      <c r="AN16" s="24"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="24"/>
+      <c r="AR16" s="24"/>
+      <c r="AS16" s="25"/>
+      <c r="AT16" s="24"/>
+      <c r="AU16" s="24"/>
+      <c r="AV16" s="24"/>
+      <c r="AW16" s="28"/>
+    </row>
+    <row r="17" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="50"/>
+      <c r="U17" s="50"/>
+      <c r="V17" s="51"/>
+      <c r="W17" s="50"/>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="50"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="6"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
-      <c r="AG17" s="8"/>
+      <c r="AG17" s="6"/>
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
-      <c r="AK17" s="8"/>
+      <c r="AK17" s="6"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
-      <c r="AO17" s="8"/>
+      <c r="AO17" s="6"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
-      <c r="AS17" s="8"/>
+      <c r="AS17" s="6"/>
       <c r="AT17" s="1"/>
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="5"/>
     </row>
-    <row r="18" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+    <row r="18" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="37"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="31"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="22"/>
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
-      <c r="Y18" s="9"/>
+      <c r="Y18" s="7"/>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
-      <c r="AC18" s="9"/>
+      <c r="AC18" s="7"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
-      <c r="AG18" s="9"/>
+      <c r="AG18" s="7"/>
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
       <c r="AJ18" s="2"/>
-      <c r="AK18" s="9"/>
+      <c r="AK18" s="7"/>
       <c r="AL18" s="2"/>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
-      <c r="AO18" s="9"/>
+      <c r="AO18" s="7"/>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="2"/>
       <c r="AR18" s="2"/>
-      <c r="AS18" s="9"/>
+      <c r="AS18" s="7"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="4"/>
     </row>
-    <row r="19" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="37" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="8"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="8"/>
+      <c r="I19" s="6"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="8"/>
+      <c r="M19" s="6"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="29"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="21"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="8"/>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="6"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AG19" s="8"/>
+      <c r="AG19" s="6"/>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
-      <c r="AK19" s="8"/>
+      <c r="AK19" s="6"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
-      <c r="AO19" s="8"/>
+      <c r="AO19" s="6"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
-      <c r="AS19" s="8"/>
+      <c r="AS19" s="6"/>
       <c r="AT19" s="1"/>
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="5"/>
     </row>
-    <row r="20" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+    <row r="20" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="9"/>
+      <c r="I20" s="7"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
-      <c r="M20" s="9"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="28"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="20"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
-      <c r="Y20" s="9"/>
+      <c r="Y20" s="7"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
-      <c r="AC20" s="9"/>
+      <c r="AC20" s="7"/>
       <c r="AD20" s="2"/>
       <c r="AE20" s="2"/>
       <c r="AF20" s="2"/>
-      <c r="AG20" s="9"/>
+      <c r="AG20" s="7"/>
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
-      <c r="AK20" s="9"/>
+      <c r="AK20" s="7"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
-      <c r="AO20" s="9"/>
+      <c r="AO20" s="7"/>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
       <c r="AR20" s="2"/>
-      <c r="AS20" s="9"/>
+      <c r="AS20" s="7"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="4"/>
     </row>
-    <row r="21" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
-      <c r="AC21" s="17"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="17"/>
-      <c r="AH21" s="16"/>
-      <c r="AI21" s="16"/>
-      <c r="AJ21" s="16"/>
-      <c r="AK21" s="17"/>
-      <c r="AL21" s="16"/>
-      <c r="AM21" s="16"/>
-      <c r="AN21" s="16"/>
-      <c r="AO21" s="17"/>
-      <c r="AP21" s="16"/>
-      <c r="AQ21" s="16"/>
-      <c r="AR21" s="16"/>
-      <c r="AS21" s="17"/>
-      <c r="AT21" s="16"/>
-      <c r="AU21" s="16"/>
-      <c r="AV21" s="16"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="11"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="11"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="11"/>
+      <c r="AI21" s="11"/>
+      <c r="AJ21" s="11"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="11"/>
+      <c r="AM21" s="11"/>
+      <c r="AN21" s="11"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="11"/>
+      <c r="AQ21" s="11"/>
+      <c r="AR21" s="11"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="11"/>
+      <c r="AU21" s="11"/>
+      <c r="AV21" s="11"/>
       <c r="AW21" s="3"/>
     </row>
-    <row r="22" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
-      <c r="T22" s="37"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="35"/>
-      <c r="AE22" s="35"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="36"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="35"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="36"/>
-      <c r="AL22" s="35"/>
-      <c r="AM22" s="35"/>
-      <c r="AN22" s="35"/>
-      <c r="AO22" s="36"/>
-      <c r="AP22" s="35"/>
-      <c r="AQ22" s="35"/>
-      <c r="AR22" s="35"/>
-      <c r="AS22" s="36"/>
-      <c r="AT22" s="35"/>
-      <c r="AU22" s="35"/>
-      <c r="AV22" s="35"/>
-      <c r="AW22" s="39"/>
-    </row>
-    <row r="23" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+    <row r="22" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="38"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="24"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="24"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="24"/>
+      <c r="AJ22" s="24"/>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="24"/>
+      <c r="AM22" s="24"/>
+      <c r="AN22" s="24"/>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="24"/>
+      <c r="AQ22" s="24"/>
+      <c r="AR22" s="24"/>
+      <c r="AS22" s="25"/>
+      <c r="AT22" s="24"/>
+      <c r="AU22" s="24"/>
+      <c r="AV22" s="24"/>
+      <c r="AW22" s="28"/>
+    </row>
+    <row r="23" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="8"/>
+      <c r="I23" s="6"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="29"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="21"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="8"/>
+      <c r="Y23" s="6"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="6"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AG23" s="8"/>
+      <c r="AG23" s="6"/>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
-      <c r="AK23" s="8"/>
+      <c r="AK23" s="6"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
-      <c r="AO23" s="8"/>
+      <c r="AO23" s="6"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
-      <c r="AS23" s="8"/>
+      <c r="AS23" s="6"/>
       <c r="AT23" s="1"/>
       <c r="AU23" s="1"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="5"/>
     </row>
-    <row r="24" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+    <row r="24" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="46"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="9"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="9"/>
+      <c r="I24" s="7"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
       <c r="P24" s="2"/>
-      <c r="Q24" s="9"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="28"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="20"/>
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
-      <c r="Y24" s="9"/>
+      <c r="Y24" s="7"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
-      <c r="AC24" s="9"/>
+      <c r="AC24" s="7"/>
       <c r="AD24" s="2"/>
       <c r="AE24" s="2"/>
       <c r="AF24" s="2"/>
-      <c r="AG24" s="9"/>
+      <c r="AG24" s="7"/>
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2"/>
-      <c r="AK24" s="9"/>
+      <c r="AK24" s="7"/>
       <c r="AL24" s="2"/>
       <c r="AM24" s="2"/>
       <c r="AN24" s="2"/>
-      <c r="AO24" s="9"/>
+      <c r="AO24" s="7"/>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="2"/>
       <c r="AR24" s="2"/>
-      <c r="AS24" s="9"/>
+      <c r="AS24" s="7"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="4"/>
     </row>
-    <row r="25" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+    <row r="25" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="17"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="16"/>
-      <c r="AF25" s="16"/>
-      <c r="AG25" s="17"/>
-      <c r="AH25" s="16"/>
-      <c r="AI25" s="16"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="17"/>
-      <c r="AL25" s="16"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="17"/>
-      <c r="AP25" s="16"/>
-      <c r="AQ25" s="16"/>
-      <c r="AR25" s="16"/>
-      <c r="AS25" s="17"/>
-      <c r="AT25" s="16"/>
-      <c r="AU25" s="16"/>
-      <c r="AV25" s="16"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="12"/>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="12"/>
+      <c r="AH25" s="11"/>
+      <c r="AI25" s="11"/>
+      <c r="AJ25" s="11"/>
+      <c r="AK25" s="12"/>
+      <c r="AL25" s="11"/>
+      <c r="AM25" s="11"/>
+      <c r="AN25" s="11"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="11"/>
+      <c r="AQ25" s="11"/>
+      <c r="AR25" s="11"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="11"/>
+      <c r="AU25" s="11"/>
+      <c r="AV25" s="11"/>
       <c r="AW25" s="3"/>
     </row>
-    <row r="26" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
+    <row r="26" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="48"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="6"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="8"/>
+      <c r="I26" s="6"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="8"/>
+      <c r="Q26" s="6"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="29"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="21"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="8"/>
+      <c r="Y26" s="6"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="6"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AG26" s="8"/>
+      <c r="AG26" s="6"/>
       <c r="AH26" s="1"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
-      <c r="AK26" s="8"/>
+      <c r="AK26" s="6"/>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
-      <c r="AO26" s="8"/>
+      <c r="AO26" s="6"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
-      <c r="AS26" s="8"/>
+      <c r="AS26" s="6"/>
       <c r="AT26" s="1"/>
       <c r="AU26" s="1"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="5"/>
     </row>
-    <row r="27" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+    <row r="27" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="20"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="16"/>
-      <c r="AI27" s="16"/>
-      <c r="AJ27" s="16"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="16"/>
-      <c r="AM27" s="16"/>
-      <c r="AN27" s="16"/>
-      <c r="AO27" s="17"/>
-      <c r="AP27" s="16"/>
-      <c r="AQ27" s="16"/>
-      <c r="AR27" s="16"/>
-      <c r="AS27" s="17"/>
-      <c r="AT27" s="16"/>
-      <c r="AU27" s="16"/>
-      <c r="AV27" s="16"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="49"/>
+      <c r="AH27" s="11"/>
+      <c r="AI27" s="11"/>
+      <c r="AJ27" s="11"/>
+      <c r="AK27" s="12"/>
+      <c r="AL27" s="11"/>
+      <c r="AM27" s="11"/>
+      <c r="AN27" s="11"/>
+      <c r="AO27" s="12"/>
+      <c r="AP27" s="11"/>
+      <c r="AQ27" s="11"/>
+      <c r="AR27" s="11"/>
+      <c r="AS27" s="12"/>
+      <c r="AT27" s="11"/>
+      <c r="AU27" s="11"/>
+      <c r="AV27" s="11"/>
       <c r="AW27" s="3"/>
     </row>
-    <row r="28" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="54"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="36"/>
-      <c r="AD28" s="35"/>
-      <c r="AE28" s="35"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="36"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="35"/>
-      <c r="AJ28" s="35"/>
-      <c r="AK28" s="36"/>
-      <c r="AL28" s="35"/>
-      <c r="AM28" s="35"/>
-      <c r="AN28" s="35"/>
-      <c r="AO28" s="36"/>
-      <c r="AP28" s="35"/>
-      <c r="AQ28" s="35"/>
-      <c r="AR28" s="35"/>
-      <c r="AS28" s="36"/>
-      <c r="AT28" s="35"/>
-      <c r="AU28" s="35"/>
-      <c r="AV28" s="35"/>
-      <c r="AW28" s="39"/>
-    </row>
-    <row r="29" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="28" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="47"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
+      <c r="AB28" s="24"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="24"/>
+      <c r="AE28" s="24"/>
+      <c r="AF28" s="24"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="24"/>
+      <c r="AI28" s="24"/>
+      <c r="AJ28" s="24"/>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="24"/>
+      <c r="AM28" s="24"/>
+      <c r="AN28" s="24"/>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="24"/>
+      <c r="AQ28" s="24"/>
+      <c r="AR28" s="24"/>
+      <c r="AS28" s="25"/>
+      <c r="AT28" s="24"/>
+      <c r="AU28" s="24"/>
+      <c r="AV28" s="24"/>
+      <c r="AW28" s="28"/>
+    </row>
+    <row r="29" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="8"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="8"/>
+      <c r="I29" s="6"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="32"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="23"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="8"/>
+      <c r="Y29" s="6"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="6"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="8"/>
+      <c r="AG29" s="6"/>
       <c r="AH29" s="1"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
-      <c r="AK29" s="8"/>
+      <c r="AK29" s="6"/>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
-      <c r="AO29" s="8"/>
+      <c r="AO29" s="6"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
-      <c r="AS29" s="8"/>
+      <c r="AS29" s="6"/>
       <c r="AT29" s="1"/>
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
       <c r="AW29" s="5"/>
     </row>
-    <row r="30" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="37"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="9"/>
+      <c r="E30" s="7"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="28"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="20"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
-      <c r="Y30" s="9"/>
+      <c r="Y30" s="7"/>
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
       <c r="AB30" s="2"/>
-      <c r="AC30" s="9"/>
+      <c r="AC30" s="7"/>
       <c r="AD30" s="2"/>
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
-      <c r="AG30" s="9"/>
+      <c r="AG30" s="7"/>
       <c r="AH30" s="2"/>
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
-      <c r="AK30" s="9"/>
+      <c r="AK30" s="7"/>
       <c r="AL30" s="2"/>
       <c r="AM30" s="2"/>
       <c r="AN30" s="2"/>
-      <c r="AO30" s="9"/>
+      <c r="AO30" s="7"/>
       <c r="AP30" s="2"/>
       <c r="AQ30" s="2"/>
       <c r="AR30" s="2"/>
-      <c r="AS30" s="9"/>
+      <c r="AS30" s="7"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="4"/>
     </row>
-    <row r="31" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="8"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="8"/>
+      <c r="I31" s="6"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="29"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="49"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="49"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="21"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="8"/>
+      <c r="Y31" s="6"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="6"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="8"/>
+      <c r="AG31" s="6"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
-      <c r="AK31" s="8"/>
+      <c r="AK31" s="6"/>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
       <c r="AN31" s="1"/>
-      <c r="AO31" s="8"/>
+      <c r="AO31" s="6"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
-      <c r="AS31" s="8"/>
+      <c r="AS31" s="6"/>
       <c r="AT31" s="1"/>
       <c r="AU31" s="1"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="5"/>
     </row>
-    <row r="32" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
+    <row r="32" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="9"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="9"/>
+      <c r="I32" s="7"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="28"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="20"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
-      <c r="Y32" s="9"/>
+      <c r="Y32" s="7"/>
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
-      <c r="AC32" s="9"/>
+      <c r="AC32" s="7"/>
       <c r="AD32" s="2"/>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
-      <c r="AG32" s="9"/>
+      <c r="AG32" s="7"/>
       <c r="AH32" s="2"/>
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
-      <c r="AK32" s="9"/>
+      <c r="AK32" s="7"/>
       <c r="AL32" s="2"/>
       <c r="AM32" s="2"/>
       <c r="AN32" s="2"/>
-      <c r="AO32" s="9"/>
+      <c r="AO32" s="7"/>
       <c r="AP32" s="2"/>
       <c r="AQ32" s="2"/>
       <c r="AR32" s="2"/>
-      <c r="AS32" s="9"/>
+      <c r="AS32" s="7"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="4"/>
     </row>
-    <row r="33" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="8"/>
+      <c r="I33" s="6"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="8"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="6"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="29"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="21"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="8"/>
+      <c r="Y33" s="6"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="6"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="8"/>
+      <c r="AG33" s="6"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
-      <c r="AK33" s="8"/>
+      <c r="AK33" s="6"/>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
       <c r="AN33" s="1"/>
-      <c r="AO33" s="8"/>
+      <c r="AO33" s="6"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
-      <c r="AS33" s="8"/>
+      <c r="AS33" s="6"/>
       <c r="AT33" s="1"/>
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="5"/>
     </row>
-    <row r="34" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
+    <row r="34" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="37"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="9"/>
+      <c r="E34" s="7"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="9"/>
+      <c r="I34" s="7"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="9"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="7"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="28"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="20"/>
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
-      <c r="Y34" s="9"/>
+      <c r="Y34" s="7"/>
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
       <c r="AB34" s="2"/>
-      <c r="AC34" s="9"/>
+      <c r="AC34" s="7"/>
       <c r="AD34" s="2"/>
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
-      <c r="AG34" s="9"/>
+      <c r="AG34" s="7"/>
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
-      <c r="AK34" s="9"/>
+      <c r="AK34" s="7"/>
       <c r="AL34" s="2"/>
       <c r="AM34" s="2"/>
       <c r="AN34" s="2"/>
-      <c r="AO34" s="9"/>
+      <c r="AO34" s="7"/>
       <c r="AP34" s="2"/>
       <c r="AQ34" s="2"/>
       <c r="AR34" s="2"/>
-      <c r="AS34" s="9"/>
+      <c r="AS34" s="7"/>
       <c r="AT34" s="2"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="4"/>
     </row>
-    <row r="35" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="37" t="s">
         <v>26</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="8"/>
+      <c r="I35" s="6"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="6"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="8"/>
+      <c r="AG35" s="6"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
-      <c r="AK35" s="8"/>
+      <c r="AK35" s="6"/>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
       <c r="AN35" s="1"/>
-      <c r="AO35" s="8"/>
+      <c r="AO35" s="6"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
-      <c r="AS35" s="8"/>
+      <c r="AS35" s="6"/>
       <c r="AT35" s="1"/>
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="5"/>
     </row>
-    <row r="36" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
+    <row r="36" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="9"/>
+      <c r="E36" s="7"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="9"/>
+      <c r="I36" s="7"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="31"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="22"/>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
-      <c r="Y36" s="9"/>
+      <c r="Y36" s="7"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
       <c r="AB36" s="2"/>
-      <c r="AC36" s="9"/>
+      <c r="AC36" s="7"/>
       <c r="AD36" s="2"/>
       <c r="AE36" s="2"/>
       <c r="AF36" s="2"/>
-      <c r="AG36" s="9"/>
+      <c r="AG36" s="7"/>
       <c r="AH36" s="2"/>
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
-      <c r="AK36" s="9"/>
+      <c r="AK36" s="7"/>
       <c r="AL36" s="2"/>
       <c r="AM36" s="2"/>
       <c r="AN36" s="2"/>
-      <c r="AO36" s="9"/>
+      <c r="AO36" s="7"/>
       <c r="AP36" s="2"/>
       <c r="AQ36" s="2"/>
       <c r="AR36" s="2"/>
-      <c r="AS36" s="9"/>
+      <c r="AS36" s="7"/>
       <c r="AT36" s="2"/>
       <c r="AU36" s="2"/>
       <c r="AV36" s="2"/>
       <c r="AW36" s="4"/>
     </row>
-    <row r="37" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="37" t="s">
         <v>27</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="6"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="8"/>
+      <c r="M37" s="6"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="20"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="49"/>
+      <c r="Y37" s="49"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="49"/>
+      <c r="AC37" s="49"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="8"/>
+      <c r="AG37" s="6"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
-      <c r="AK37" s="8"/>
+      <c r="AK37" s="6"/>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
       <c r="AN37" s="1"/>
-      <c r="AO37" s="8"/>
+      <c r="AO37" s="6"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
-      <c r="AS37" s="8"/>
+      <c r="AS37" s="6"/>
       <c r="AT37" s="1"/>
       <c r="AU37" s="1"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="5"/>
     </row>
-    <row r="38" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
+    <row r="38" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="37"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="9"/>
+      <c r="E38" s="7"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="9"/>
+      <c r="I38" s="7"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-      <c r="M38" s="9"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-      <c r="Q38" s="9"/>
+      <c r="Q38" s="7"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="28"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="20"/>
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
-      <c r="Y38" s="9"/>
+      <c r="Y38" s="7"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
       <c r="AB38" s="2"/>
-      <c r="AC38" s="9"/>
+      <c r="AC38" s="7"/>
       <c r="AD38" s="2"/>
       <c r="AE38" s="2"/>
       <c r="AF38" s="2"/>
-      <c r="AG38" s="9"/>
+      <c r="AG38" s="7"/>
       <c r="AH38" s="2"/>
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
-      <c r="AK38" s="9"/>
+      <c r="AK38" s="7"/>
       <c r="AL38" s="2"/>
       <c r="AM38" s="2"/>
       <c r="AN38" s="2"/>
-      <c r="AO38" s="9"/>
+      <c r="AO38" s="7"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
-      <c r="AS38" s="9"/>
+      <c r="AS38" s="7"/>
       <c r="AT38" s="2"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
       <c r="AW38" s="4"/>
     </row>
-    <row r="39" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="8"/>
+      <c r="I39" s="6"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="8"/>
+      <c r="M39" s="6"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="8"/>
+      <c r="Q39" s="6"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="29"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="21"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="Y39" s="8"/>
+      <c r="Y39" s="6"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="20"/>
-      <c r="AD39" s="20"/>
-      <c r="AE39" s="20"/>
-      <c r="AF39" s="20"/>
-      <c r="AG39" s="20"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="49"/>
+      <c r="AF39" s="49"/>
+      <c r="AG39" s="49"/>
       <c r="AH39" s="1"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
-      <c r="AK39" s="8"/>
+      <c r="AK39" s="6"/>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
       <c r="AN39" s="1"/>
-      <c r="AO39" s="8"/>
+      <c r="AO39" s="6"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
       <c r="AR39" s="1"/>
-      <c r="AS39" s="8"/>
+      <c r="AS39" s="6"/>
       <c r="AT39" s="1"/>
       <c r="AU39" s="1"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="5"/>
     </row>
-    <row r="40" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
+    <row r="40" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="37"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="9"/>
+      <c r="E40" s="7"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="9"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-      <c r="M40" s="9"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-      <c r="Q40" s="9"/>
+      <c r="Q40" s="7"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="28"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="20"/>
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
-      <c r="Y40" s="9"/>
+      <c r="Y40" s="7"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
       <c r="AB40" s="2"/>
-      <c r="AC40" s="9"/>
+      <c r="AC40" s="7"/>
       <c r="AD40" s="2"/>
       <c r="AE40" s="2"/>
       <c r="AF40" s="2"/>
-      <c r="AG40" s="9"/>
+      <c r="AG40" s="7"/>
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="9"/>
+      <c r="AK40" s="7"/>
       <c r="AL40" s="2"/>
       <c r="AM40" s="2"/>
       <c r="AN40" s="2"/>
-      <c r="AO40" s="9"/>
+      <c r="AO40" s="7"/>
       <c r="AP40" s="2"/>
       <c r="AQ40" s="2"/>
       <c r="AR40" s="2"/>
-      <c r="AS40" s="9"/>
+      <c r="AS40" s="7"/>
       <c r="AT40" s="2"/>
       <c r="AU40" s="2"/>
       <c r="AV40" s="2"/>
       <c r="AW40" s="4"/>
     </row>
-    <row r="41" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="27"/>
-      <c r="W41" s="16"/>
-      <c r="X41" s="16"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="16"/>
-      <c r="AA41" s="16"/>
-      <c r="AB41" s="16"/>
-      <c r="AC41" s="17"/>
-      <c r="AD41" s="16"/>
-      <c r="AE41" s="16"/>
-      <c r="AF41" s="20"/>
-      <c r="AG41" s="20"/>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="20"/>
-      <c r="AJ41" s="20"/>
-      <c r="AK41" s="20"/>
-      <c r="AL41" s="16"/>
-      <c r="AM41" s="16"/>
-      <c r="AN41" s="16"/>
-      <c r="AO41" s="17"/>
-      <c r="AP41" s="16"/>
-      <c r="AQ41" s="16"/>
-      <c r="AR41" s="16"/>
-      <c r="AS41" s="17"/>
-      <c r="AT41" s="16"/>
-      <c r="AU41" s="16"/>
-      <c r="AV41" s="16"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="12"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="12"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11"/>
+      <c r="AB41" s="11"/>
+      <c r="AC41" s="12"/>
+      <c r="AD41" s="11"/>
+      <c r="AE41" s="11"/>
+      <c r="AF41" s="49"/>
+      <c r="AG41" s="49"/>
+      <c r="AH41" s="49"/>
+      <c r="AI41" s="49"/>
+      <c r="AJ41" s="49"/>
+      <c r="AK41" s="49"/>
+      <c r="AL41" s="11"/>
+      <c r="AM41" s="11"/>
+      <c r="AN41" s="11"/>
+      <c r="AO41" s="12"/>
+      <c r="AP41" s="11"/>
+      <c r="AQ41" s="11"/>
+      <c r="AR41" s="11"/>
+      <c r="AS41" s="12"/>
+      <c r="AT41" s="11"/>
+      <c r="AU41" s="11"/>
+      <c r="AV41" s="11"/>
       <c r="AW41" s="3"/>
     </row>
-    <row r="42" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="34"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="44"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="44"/>
-      <c r="R42" s="43"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="43"/>
-      <c r="U42" s="44"/>
-      <c r="V42" s="47"/>
-      <c r="W42" s="35"/>
-      <c r="X42" s="35"/>
-      <c r="Y42" s="36"/>
-      <c r="Z42" s="35"/>
-      <c r="AA42" s="35"/>
-      <c r="AB42" s="35"/>
-      <c r="AC42" s="36"/>
-      <c r="AD42" s="35"/>
-      <c r="AE42" s="35"/>
-      <c r="AF42" s="35"/>
-      <c r="AG42" s="36"/>
-      <c r="AH42" s="43"/>
-      <c r="AI42" s="43"/>
-      <c r="AJ42" s="43"/>
-      <c r="AK42" s="44"/>
-      <c r="AL42" s="43"/>
-      <c r="AM42" s="35"/>
-      <c r="AN42" s="35"/>
-      <c r="AO42" s="36"/>
-      <c r="AP42" s="35"/>
-      <c r="AQ42" s="35"/>
-      <c r="AR42" s="35"/>
-      <c r="AS42" s="36"/>
-      <c r="AT42" s="35"/>
-      <c r="AU42" s="35"/>
-      <c r="AV42" s="35"/>
-      <c r="AW42" s="39"/>
-    </row>
-    <row r="43" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="52" t="s">
+    <row r="42" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="38"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="24"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="25"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="31"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="25"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
+      <c r="AR42" s="24"/>
+      <c r="AS42" s="25"/>
+      <c r="AT42" s="24"/>
+      <c r="AU42" s="24"/>
+      <c r="AV42" s="24"/>
+      <c r="AW42" s="28"/>
+    </row>
+    <row r="43" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="6"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="8"/>
+      <c r="I43" s="6"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="41"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="50"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="50"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="51"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Y43" s="8"/>
+      <c r="Y43" s="6"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="6"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="18"/>
-      <c r="AL43" s="18"/>
+      <c r="AH43" s="50"/>
+      <c r="AI43" s="50"/>
+      <c r="AJ43" s="50"/>
+      <c r="AK43" s="50"/>
+      <c r="AL43" s="50"/>
       <c r="AM43" s="1"/>
       <c r="AN43" s="1"/>
-      <c r="AO43" s="8"/>
+      <c r="AO43" s="6"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
-      <c r="AS43" s="8"/>
+      <c r="AS43" s="6"/>
       <c r="AT43" s="1"/>
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="5"/>
     </row>
-    <row r="44" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53"/>
+    <row r="44" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="46"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="7"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="9"/>
+      <c r="I44" s="7"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
-      <c r="T44" s="19"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="28"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
+      <c r="R44" s="13"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="13"/>
+      <c r="U44" s="13"/>
+      <c r="V44" s="20"/>
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
-      <c r="Y44" s="9"/>
+      <c r="Y44" s="7"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
       <c r="AB44" s="2"/>
-      <c r="AC44" s="9"/>
+      <c r="AC44" s="7"/>
       <c r="AD44" s="2"/>
       <c r="AE44" s="2"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="8"/>
+      <c r="AG44" s="6"/>
       <c r="AH44" s="1"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
-      <c r="AK44" s="8"/>
+      <c r="AK44" s="6"/>
       <c r="AL44" s="2"/>
       <c r="AM44" s="2"/>
       <c r="AN44" s="2"/>
-      <c r="AO44" s="9"/>
+      <c r="AO44" s="7"/>
       <c r="AP44" s="2"/>
       <c r="AQ44" s="2"/>
       <c r="AR44" s="2"/>
-      <c r="AS44" s="9"/>
+      <c r="AS44" s="7"/>
       <c r="AT44" s="2"/>
       <c r="AU44" s="2"/>
       <c r="AV44" s="2"/>
       <c r="AW44" s="4"/>
     </row>
-    <row r="45" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53" t="s">
+    <row r="45" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="46" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="8"/>
+      <c r="E45" s="6"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="8"/>
+      <c r="I45" s="6"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="8"/>
+      <c r="M45" s="6"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="8"/>
+      <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="20"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="49"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="8"/>
+      <c r="Y45" s="6"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="6"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
-      <c r="AF45" s="16"/>
-      <c r="AG45" s="17"/>
-      <c r="AH45" s="20"/>
-      <c r="AI45" s="20"/>
-      <c r="AJ45" s="20"/>
-      <c r="AK45" s="20"/>
-      <c r="AL45" s="20"/>
+      <c r="AF45" s="11"/>
+      <c r="AG45" s="12"/>
+      <c r="AH45" s="49"/>
+      <c r="AI45" s="49"/>
+      <c r="AJ45" s="49"/>
+      <c r="AK45" s="49"/>
+      <c r="AL45" s="49"/>
       <c r="AM45" s="1"/>
       <c r="AN45" s="1"/>
-      <c r="AO45" s="8"/>
+      <c r="AO45" s="6"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
-      <c r="AS45" s="8"/>
+      <c r="AS45" s="6"/>
       <c r="AT45" s="1"/>
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="5"/>
     </row>
-    <row r="46" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+    <row r="46" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="46"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="9"/>
+      <c r="E46" s="7"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="9"/>
+      <c r="I46" s="7"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
-      <c r="M46" s="9"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
-      <c r="Q46" s="9"/>
+      <c r="Q46" s="7"/>
       <c r="R46" s="2"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
-      <c r="V46" s="31"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
+      <c r="U46" s="13"/>
+      <c r="V46" s="22"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
-      <c r="Y46" s="9"/>
+      <c r="Y46" s="7"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
-      <c r="AC46" s="9"/>
+      <c r="AC46" s="7"/>
       <c r="AD46" s="2"/>
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
-      <c r="AG46" s="9"/>
+      <c r="AG46" s="7"/>
       <c r="AH46" s="2"/>
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
-      <c r="AK46" s="9"/>
+      <c r="AK46" s="7"/>
       <c r="AL46" s="2"/>
       <c r="AM46" s="2"/>
       <c r="AN46" s="2"/>
-      <c r="AO46" s="9"/>
+      <c r="AO46" s="7"/>
       <c r="AP46" s="2"/>
       <c r="AQ46" s="2"/>
       <c r="AR46" s="2"/>
-      <c r="AS46" s="9"/>
+      <c r="AS46" s="7"/>
       <c r="AT46" s="2"/>
       <c r="AU46" s="2"/>
       <c r="AV46" s="2"/>
       <c r="AW46" s="4"/>
     </row>
-    <row r="47" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
+    <row r="47" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="39"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3506,7 +3494,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="29"/>
+      <c r="V47" s="21"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -3535,8 +3523,8 @@
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
     </row>
-    <row r="48" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
+    <row r="48" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="39"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3556,12 +3544,12 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="33" t="s">
+      <c r="U48" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
+      <c r="V48" s="40"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="40"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -3588,8 +3576,8 @@
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
     </row>
-    <row r="49" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
+    <row r="49" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="39"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3639,8 +3627,8 @@
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
     </row>
-    <row r="50" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+    <row r="50" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="39"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3690,8 +3678,8 @@
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
     </row>
-    <row r="51" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+    <row r="51" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="39"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3741,8 +3729,8 @@
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
     </row>
-    <row r="52" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
+    <row r="52" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="39"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3792,8 +3780,8 @@
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
     </row>
-    <row r="53" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+    <row r="53" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="39"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3843,8 +3831,8 @@
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
     </row>
-    <row r="54" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
+    <row r="54" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="39"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3894,8 +3882,8 @@
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
     </row>
-    <row r="55" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
+    <row r="55" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="39"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -3945,8 +3933,8 @@
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
     </row>
-    <row r="56" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
+    <row r="56" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="39"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -3996,8 +3984,8 @@
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
     </row>
-    <row r="57" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
+    <row r="57" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="39"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -4047,8 +4035,8 @@
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
     </row>
-    <row r="58" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
+    <row r="58" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="39"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -4098,8 +4086,8 @@
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
     </row>
-    <row r="59" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
+    <row r="59" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="39"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -4149,8 +4137,8 @@
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
     </row>
-    <row r="60" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
+    <row r="60" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="39"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -4200,8 +4188,8 @@
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
     </row>
-    <row r="61" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
+    <row r="61" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="39"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -4251,8 +4239,8 @@
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
     </row>
-    <row r="62" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
+    <row r="62" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="39"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -4302,8 +4290,8 @@
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
     </row>
-    <row r="63" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+    <row r="63" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="39"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4353,8 +4341,8 @@
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
     </row>
-    <row r="64" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
+    <row r="64" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="39"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4404,8 +4392,8 @@
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
     </row>
-    <row r="65" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
+    <row r="65" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="39"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4455,8 +4443,8 @@
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
     </row>
-    <row r="66" spans="1:49" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
+    <row r="66" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="39"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4519,11 +4507,6 @@
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
@@ -4531,6 +4514,11 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
@@ -4541,13 +4529,13 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AP2:AS2"/>
+    <mergeCell ref="AT2:AW2"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="Z2:AC2"/>
     <mergeCell ref="AD2:AG2"/>
     <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="AP2:AS2"/>
-    <mergeCell ref="AT2:AW2"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:M2"/>

--- a/Diagrams/Gantt chart/專案甘特圖.xlsx
+++ b/Diagrams/Gantt chart/專案甘特圖.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\Diagrams\Gantt chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A91CE24-2D64-495D-9751-7A0A4153C013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32B479B-FFAD-4589-925D-64E4D2EFBE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC956E1D-17AA-4CE2-B07B-3D8F95ED7E8C}"/>
   </bookViews>
@@ -247,12 +247,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E0E3"/>
+        <fgColor rgb="FFC8D2D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -536,13 +536,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,48 +657,48 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -700,6 +709,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -710,6 +728,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC8D2D6"/>
       <color rgb="FFD9E0E3"/>
       <color rgb="FFE2E8EA"/>
       <color rgb="FF607D8B"/>
@@ -1055,137 +1074,137 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
+      <c r="AJ1" s="45"/>
+      <c r="AK1" s="45"/>
+      <c r="AL1" s="45"/>
+      <c r="AM1" s="45"/>
+      <c r="AN1" s="45"/>
+      <c r="AO1" s="45"/>
+      <c r="AP1" s="45"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="45"/>
+      <c r="AS1" s="45"/>
+      <c r="AT1" s="45"/>
+      <c r="AU1" s="45"/>
+      <c r="AV1" s="45"/>
+      <c r="AW1" s="45"/>
     </row>
     <row r="2" spans="1:49" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43" t="s">
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43" t="s">
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43" t="s">
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43" t="s">
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43" t="s">
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="47"/>
+      <c r="AD2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43" t="s">
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="47"/>
+      <c r="AG2" s="47"/>
+      <c r="AH2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43" t="s">
+      <c r="AI2" s="47"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43" t="s">
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="47"/>
+      <c r="AP2" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="43"/>
-      <c r="AT2" s="43" t="s">
+      <c r="AQ2" s="47"/>
+      <c r="AR2" s="47"/>
+      <c r="AS2" s="47"/>
+      <c r="AT2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="AU2" s="43"/>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="44"/>
+      <c r="AU2" s="47"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="48"/>
     </row>
     <row r="3" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="46" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="49"/>
@@ -1238,7 +1257,7 @@
       <c r="AW3" s="5"/>
     </row>
     <row r="4" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -1289,7 +1308,7 @@
       <c r="AW4" s="4"/>
     </row>
     <row r="5" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="1"/>
@@ -1342,7 +1361,7 @@
       <c r="AW5" s="5"/>
     </row>
     <row r="6" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="13"/>
@@ -1393,7 +1412,7 @@
       <c r="AW6" s="4"/>
     </row>
     <row r="7" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="42" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1"/>
@@ -1446,7 +1465,7 @@
       <c r="AW7" s="5"/>
     </row>
     <row r="8" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1497,7 +1516,7 @@
       <c r="AW8" s="4"/>
     </row>
     <row r="9" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="43" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="11"/>
@@ -1550,7 +1569,7 @@
       <c r="AW9" s="3"/>
     </row>
     <row r="10" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
@@ -1601,7 +1620,7 @@
       <c r="AW10" s="28"/>
     </row>
     <row r="11" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="39" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1"/>
@@ -1654,7 +1673,7 @@
       <c r="AW11" s="5"/>
     </row>
     <row r="12" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1705,7 +1724,7 @@
       <c r="AW12" s="4"/>
     </row>
     <row r="13" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="38" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1"/>
@@ -1758,7 +1777,7 @@
       <c r="AW13" s="5"/>
     </row>
     <row r="14" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1809,7 +1828,7 @@
       <c r="AW14" s="4"/>
     </row>
     <row r="15" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="38" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="11"/>
@@ -1862,7 +1881,7 @@
       <c r="AW15" s="3"/>
     </row>
     <row r="16" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47"/>
+      <c r="A16" s="41"/>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
@@ -1913,7 +1932,7 @@
       <c r="AW16" s="28"/>
     </row>
     <row r="17" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="42" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1"/>
@@ -1940,10 +1959,10 @@
       <c r="W17" s="50"/>
       <c r="X17" s="50"/>
       <c r="Y17" s="50"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="6"/>
+      <c r="Z17" s="50"/>
+      <c r="AA17" s="50"/>
+      <c r="AB17" s="50"/>
+      <c r="AC17" s="50"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
@@ -1966,7 +1985,7 @@
       <c r="AW17" s="5"/>
     </row>
     <row r="18" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2017,7 +2036,7 @@
       <c r="AW18" s="4"/>
     </row>
     <row r="19" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="43" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1"/>
@@ -2070,7 +2089,7 @@
       <c r="AW19" s="5"/>
     </row>
     <row r="20" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2121,7 +2140,7 @@
       <c r="AW20" s="4"/>
     </row>
     <row r="21" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="43" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="11"/>
@@ -2174,7 +2193,7 @@
       <c r="AW21" s="3"/>
     </row>
     <row r="22" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="24"/>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
@@ -2225,7 +2244,7 @@
       <c r="AW22" s="28"/>
     </row>
     <row r="23" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="1"/>
@@ -2278,7 +2297,7 @@
       <c r="AW23" s="5"/>
     </row>
     <row r="24" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
+      <c r="A24" s="38"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2329,7 +2348,7 @@
       <c r="AW24" s="4"/>
     </row>
     <row r="25" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="38" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="11"/>
@@ -2382,7 +2401,7 @@
       <c r="AW25" s="3"/>
     </row>
     <row r="26" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2433,7 +2452,7 @@
       <c r="AW26" s="5"/>
     </row>
     <row r="27" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="11"/>
@@ -2486,7 +2505,7 @@
       <c r="AW27" s="3"/>
     </row>
     <row r="28" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="47"/>
+      <c r="A28" s="41"/>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
@@ -2537,7 +2556,7 @@
       <c r="AW28" s="28"/>
     </row>
     <row r="29" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="42" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1"/>
@@ -2555,7 +2574,7 @@
       <c r="N29" s="50"/>
       <c r="O29" s="50"/>
       <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
+      <c r="Q29" s="55"/>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
@@ -2590,7 +2609,7 @@
       <c r="AW29" s="5"/>
     </row>
     <row r="30" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="43"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2641,7 +2660,7 @@
       <c r="AW30" s="4"/>
     </row>
     <row r="31" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="43" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="1"/>
@@ -2664,10 +2683,10 @@
       <c r="S31" s="49"/>
       <c r="T31" s="49"/>
       <c r="U31" s="49"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="6"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="49"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -2694,7 +2713,7 @@
       <c r="AW31" s="5"/>
     </row>
     <row r="32" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
+      <c r="A32" s="43"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2715,7 +2734,7 @@
       <c r="S32" s="13"/>
       <c r="T32" s="13"/>
       <c r="U32" s="13"/>
-      <c r="V32" s="20"/>
+      <c r="V32" s="22"/>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
       <c r="Y32" s="7"/>
@@ -2745,7 +2764,7 @@
       <c r="AW32" s="4"/>
     </row>
     <row r="33" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="43" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="1"/>
@@ -2798,7 +2817,7 @@
       <c r="AW33" s="5"/>
     </row>
     <row r="34" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2849,7 +2868,7 @@
       <c r="AW34" s="4"/>
     </row>
     <row r="35" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B35" s="1"/>
@@ -2902,7 +2921,7 @@
       <c r="AW35" s="5"/>
     </row>
     <row r="36" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
+      <c r="A36" s="43"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2953,7 +2972,7 @@
       <c r="AW36" s="4"/>
     </row>
     <row r="37" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
+      <c r="A37" s="43" t="s">
         <v>27</v>
       </c>
       <c r="B37" s="1"/>
@@ -3006,7 +3025,7 @@
       <c r="AW37" s="5"/>
     </row>
     <row r="38" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
+      <c r="A38" s="43"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -3057,7 +3076,7 @@
       <c r="AW38" s="4"/>
     </row>
     <row r="39" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
+      <c r="A39" s="43" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="1"/>
@@ -3092,8 +3111,8 @@
       <c r="AE39" s="49"/>
       <c r="AF39" s="49"/>
       <c r="AG39" s="49"/>
-      <c r="AH39" s="1"/>
-      <c r="AI39" s="1"/>
+      <c r="AH39" s="49"/>
+      <c r="AI39" s="49"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="6"/>
       <c r="AL39" s="1"/>
@@ -3110,7 +3129,7 @@
       <c r="AW39" s="5"/>
     </row>
     <row r="40" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
+      <c r="A40" s="43"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -3161,7 +3180,7 @@
       <c r="AW40" s="4"/>
     </row>
     <row r="41" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37" t="s">
+      <c r="A41" s="43" t="s">
         <v>29</v>
       </c>
       <c r="B41" s="11"/>
@@ -3200,10 +3219,10 @@
       <c r="AI41" s="49"/>
       <c r="AJ41" s="49"/>
       <c r="AK41" s="49"/>
-      <c r="AL41" s="11"/>
-      <c r="AM41" s="11"/>
-      <c r="AN41" s="11"/>
-      <c r="AO41" s="12"/>
+      <c r="AL41" s="49"/>
+      <c r="AM41" s="49"/>
+      <c r="AN41" s="49"/>
+      <c r="AO41" s="49"/>
       <c r="AP41" s="11"/>
       <c r="AQ41" s="11"/>
       <c r="AR41" s="11"/>
@@ -3214,7 +3233,7 @@
       <c r="AW41" s="3"/>
     </row>
     <row r="42" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="24"/>
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
@@ -3247,11 +3266,11 @@
       <c r="AE42" s="24"/>
       <c r="AF42" s="24"/>
       <c r="AG42" s="25"/>
-      <c r="AH42" s="30"/>
-      <c r="AI42" s="30"/>
-      <c r="AJ42" s="30"/>
-      <c r="AK42" s="31"/>
-      <c r="AL42" s="30"/>
+      <c r="AH42" s="53"/>
+      <c r="AI42" s="53"/>
+      <c r="AJ42" s="53"/>
+      <c r="AK42" s="54"/>
+      <c r="AL42" s="53"/>
       <c r="AM42" s="24"/>
       <c r="AN42" s="24"/>
       <c r="AO42" s="25"/>
@@ -3265,7 +3284,7 @@
       <c r="AW42" s="28"/>
     </row>
     <row r="43" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
+      <c r="A43" s="39" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1"/>
@@ -3318,7 +3337,7 @@
       <c r="AW43" s="5"/>
     </row>
     <row r="44" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="46"/>
+      <c r="A44" s="38"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -3369,7 +3388,7 @@
       <c r="AW44" s="4"/>
     </row>
     <row r="45" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="46" t="s">
+      <c r="A45" s="38" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="1"/>
@@ -3422,7 +3441,7 @@
       <c r="AW45" s="5"/>
     </row>
     <row r="46" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="46"/>
+      <c r="A46" s="38"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -3473,7 +3492,7 @@
       <c r="AW46" s="4"/>
     </row>
     <row r="47" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="39"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3524,7 +3543,7 @@
       <c r="AW47" s="1"/>
     </row>
     <row r="48" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="39"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3544,12 +3563,12 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="40" t="s">
+      <c r="U48" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="V48" s="40"/>
-      <c r="W48" s="40"/>
-      <c r="X48" s="40"/>
+      <c r="V48" s="37"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="37"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -3577,7 +3596,7 @@
       <c r="AW48" s="1"/>
     </row>
     <row r="49" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3628,7 +3647,7 @@
       <c r="AW49" s="1"/>
     </row>
     <row r="50" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="39"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3679,7 +3698,7 @@
       <c r="AW50" s="1"/>
     </row>
     <row r="51" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3730,7 +3749,7 @@
       <c r="AW51" s="1"/>
     </row>
     <row r="52" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="39"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3781,7 +3800,7 @@
       <c r="AW52" s="1"/>
     </row>
     <row r="53" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="39"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3832,7 +3851,7 @@
       <c r="AW53" s="1"/>
     </row>
     <row r="54" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
+      <c r="A54" s="36"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3883,7 +3902,7 @@
       <c r="AW54" s="1"/>
     </row>
     <row r="55" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="39"/>
+      <c r="A55" s="36"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -3934,7 +3953,7 @@
       <c r="AW55" s="1"/>
     </row>
     <row r="56" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
+      <c r="A56" s="36"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -3985,7 +4004,7 @@
       <c r="AW56" s="1"/>
     </row>
     <row r="57" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="39"/>
+      <c r="A57" s="36"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -4036,7 +4055,7 @@
       <c r="AW57" s="1"/>
     </row>
     <row r="58" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="39"/>
+      <c r="A58" s="36"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -4087,7 +4106,7 @@
       <c r="AW58" s="1"/>
     </row>
     <row r="59" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="39"/>
+      <c r="A59" s="36"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -4138,7 +4157,7 @@
       <c r="AW59" s="1"/>
     </row>
     <row r="60" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="39"/>
+      <c r="A60" s="36"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -4189,7 +4208,7 @@
       <c r="AW60" s="1"/>
     </row>
     <row r="61" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="39"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -4240,7 +4259,7 @@
       <c r="AW61" s="1"/>
     </row>
     <row r="62" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="39"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -4291,7 +4310,7 @@
       <c r="AW62" s="1"/>
     </row>
     <row r="63" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="39"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4342,7 +4361,7 @@
       <c r="AW63" s="1"/>
     </row>
     <row r="64" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="39"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4393,7 +4412,7 @@
       <c r="AW64" s="1"/>
     </row>
     <row r="65" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="39"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4444,7 +4463,7 @@
       <c r="AW65" s="1"/>
     </row>
     <row r="66" spans="1:49" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="39"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4496,17 +4515,29 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="U48:X48"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="AD2:AG2"/>
+    <mergeCell ref="AH2:AK2"/>
+    <mergeCell ref="AL2:AO2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="A1:AW1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="AP2:AS2"/>
+    <mergeCell ref="AT2:AW2"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A25:A26"/>
@@ -4519,29 +4550,17 @@
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A1:AW1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="AP2:AS2"/>
-    <mergeCell ref="AT2:AW2"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AD2:AG2"/>
-    <mergeCell ref="AH2:AK2"/>
-    <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
